--- a/corpus/md/prefiltro.xlsx
+++ b/corpus/md/prefiltro.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,7 +426,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Corrida: 2026-10-15 03:15 (los resultados varían entre corridas: algunos sitios responden distinto)</t>
+          <t>Corrida: 2026-10-28 00:41 (los resultados varían entre corridas: algunos sitios responden distinto)</t>
         </is>
       </c>
     </row>
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -524,13 +524,13 @@
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -543,10 +543,10 @@
         <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="n">
         <v>253</v>
@@ -578,10 +578,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" t="n">
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" t="n">
         <v>338</v>
@@ -672,13 +672,13 @@
         <v>53</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>71</v>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
@@ -710,13 +710,13 @@
         <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C20" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D20" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20" t="n">
         <v>259</v>
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
@@ -894,11 +894,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -909,11 +909,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Excluido a mano: paper de LLM/salud mental en bioseguridad (para revisar por Investigación)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -924,25 +924,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/salud mental en bioseguridad (para revisar por Investigación)</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Prioridad: Baja (porcino)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1273,7 +1258,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Genetic data and meteorological conditions: unravelling the windborne transmission of H5N1 high-pathogenicity avian influenza between commercial poultry outbreaks</t>
+          <t>Genetic data and meteorological conditions suggesting windborne transmission of H5N1 high-pathogenicity avian influenza between commercial poultry outbreaks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1332,34 +1317,24 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Revisar título</t>
+          <t>Caído</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>la página no tiene &lt;title&gt;</t>
+          <t>c) Web: www.biorxiv.org no disponible (HTTP 429) | c) Web: www.biorxiv.org no disponible (HTTP 429)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>c) Web</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://www.biorxiv.org/content/10.1101/2025.02.12.637829v1</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
           <t>Genetic data and meteorological conditions: unravelling the windborne transmission of H5N1 high-pathogenicity avian influenza between commercial poultry outbreaks</t>
@@ -2958,22 +2933,26 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Caído</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>d) PDF directo: sin respuesta en 10 s</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>d) PDF directo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://www.aphis.usda.gov/sites/default/files/mortalitycompostingprotocol.pdf</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr">
@@ -3479,22 +3458,26 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Caído</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>d) PDF directo: sin respuesta en 10 s</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>d) PDF directo</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://www.aphis.usda.gov/sites/default/files/avian-influenza-case-definition.pdf</t>
+        </is>
+      </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
@@ -4547,10 +4530,14 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
+          <t>Revisar título</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>la página no tiene &lt;title&gt;</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
@@ -4567,13 +4554,9 @@
           <t>https://www.who.int/es/news-room/fact-sheets/detail/influenza-(avian-and-other-zoonotic)</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Gripe aviar y otras gripes de origen zoonótico</t>
-        </is>
-      </c>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -4991,7 +4974,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5011,12 +4994,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 1.1.6: Validacion de las pruebas de diagnostico de las enfermedades infecciosas de animales terrestres</t>
+          <t>Plan de Contingencia Influenza Aviar (IA), Version 6.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>aviar</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5031,14 +5014,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/1.01.06_VALIDATION.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/Plan%20de%20Contingencia%20Chile%20Actualizado%20V.6.pdf</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>url:woah.org/fileadmin/home/eng/health_standards/tahm/1.01.06_validation.pdf</t>
+          <t>url:sag.gob.cl/sites/default/files/plan%20de%20contingencia%20chile%20actualizado%20v.6.pdf</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
@@ -5067,19 +5050,19 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/1.01.06_VALIDATION.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/Plan%20de%20Contingencia%20Chile%20Actualizado%20V.6.pdf</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 1.1.6: Validacion de las pruebas de diagnostico de las enfermedades infecciosas de animales terrestres</t>
+          <t>Plan de Contingencia Influenza Aviar (IA), Version 6.0</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>OMSA</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -5096,7 +5079,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5116,12 +5099,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 3.3.4: Influenza aviar (incluida la infeccion por los virus de la influenza aviar altamente patogenos)</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 1.1.6: Validacion de las pruebas de diagnostico de las enfermedades infecciosas de animales terrestres</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>aviar</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5136,14 +5119,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/3.03.04_AI.pdf</t>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/1.01.06_VALIDATION.pdf</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>url:woah.org/fileadmin/home/eng/health_standards/tahm/3.03.04_ai.pdf</t>
+          <t>url:woah.org/fileadmin/home/eng/health_standards/tahm/1.01.06_validation.pdf</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
@@ -5172,14 +5155,14 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/3.03.04_AI.pdf</t>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/1.01.06_VALIDATION.pdf</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 3.3.4: Influenza aviar (incluida la infeccion por los virus de la influenza aviar altamente patogenos)</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 1.1.6: Validacion de las pruebas de diagnostico de las enfermedades infecciosas de animales terrestres</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -5189,7 +5172,7 @@
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -5201,7 +5184,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5221,12 +5204,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kits aprobados por el Servicio, segun instructivo tecnico pertinente (D-ATR-AAT-096, version 01)</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 3.3.4: Influenza aviar (incluida la infeccion por los virus de la influenza aviar altamente patogenos)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>aviar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5241,14 +5224,14 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-096%20kits%20autorizados%20enf%20pecuarias%2017.08.2026.pdf</t>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/3.03.04_AI.pdf</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/sites/default/files/d-atr-aat-096%20kits%20autorizados%20enf%20pecuarias%2017.08.2026.pdf</t>
+          <t>url:woah.org/fileadmin/home/eng/health_standards/tahm/3.03.04_ai.pdf</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -5277,24 +5260,24 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-096%20kits%20autorizados%20enf%20pecuarias%2017.08.2026.pdf</t>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/3.03.04_AI.pdf</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Kits aprobados por el Servicio, segun instructivo tecnico pertinente (D-ATR-AAT-096, version 01)</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 3.3.4: Influenza aviar (incluida la infeccion por los virus de la influenza aviar altamente patogenos)</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>OMSA</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -5306,7 +5289,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5326,7 +5309,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 2.2.1: Desarrollo y optimizacion de los ensayos de deteccion de anticuerpos</t>
+          <t>Kits aprobados por el Servicio, segun instructivo tecnico pertinente (D-ATR-AAT-096, version 01)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5346,14 +5329,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/2.02.01_ANTIBODY_DETECT.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-096%20kits%20autorizados%20enf%20pecuarias%2017.08.2026.pdf</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>url:woah.org/fileadmin/home/eng/health_standards/tahm/2.02.01_antibody_detect.pdf</t>
+          <t>url:sag.gob.cl/sites/default/files/d-atr-aat-096%20kits%20autorizados%20enf%20pecuarias%2017.08.2026.pdf</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -5382,24 +5365,24 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/2.02.01_ANTIBODY_DETECT.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-096%20kits%20autorizados%20enf%20pecuarias%2017.08.2026.pdf</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 2.2.1: Desarrollo y optimizacion de los ensayos de deteccion de anticuerpos</t>
+          <t>Kits aprobados por el Servicio, segun instructivo tecnico pertinente (D-ATR-AAT-096, version 01)</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>OMSA</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -5411,7 +5394,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5431,12 +5414,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>IDEXX AI MultiS-Screen Ab Test - pagina de producto</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 2.2.1: Desarrollo y optimizacion de los ensayos de deteccion de anticuerpos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>aviar</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5446,19 +5429,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Página web con contenido</t>
+          <t>PDF directo</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/en/livestock/livestock-tests/poultry-tests/idexx-ai-multis-screen-ab-test/</t>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/2.02.01_ANTIBODY_DETECT.pdf</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>url:idexx.com/en/livestock/livestock-tests/poultry-tests/idexx-ai-multis-screen-ab-test</t>
+          <t>url:woah.org/fileadmin/home/eng/health_standards/tahm/2.02.01_antibody_detect.pdf</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
@@ -5482,35 +5465,29 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>c) Web</t>
+          <t>d) PDF directo</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/en/livestock/livestock-tests/poultry-tests/idexx-ai-multis-screen-ab-test/</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Avian Influenza (AI) MultiS-Screen Ab Test - IDEXX US</t>
-        </is>
-      </c>
-      <c r="AA41" t="n">
-        <v>75</v>
-      </c>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/2.02.01_ANTIBODY_DETECT.pdf</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>IDEXX AI MultiS-Screen Ab Test - pagina de producto</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 2.2.1: Desarrollo y optimizacion de los ensayos de deteccion de anticuerpos</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>IDEXX</t>
+          <t>OMSA</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>s.f.</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
@@ -5522,7 +5499,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>D21</t>
+          <t>D20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5542,7 +5519,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Limited detection of antibodies to clade 2.3.4.4 A/goose/Guangdong/1/1996 lineage HPAI virus in North American waterfowl</t>
+          <t>IDEXX AI MultiS-Screen Ab Test - pagina de producto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5557,23 +5534,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Artículo (web abierta)</t>
+          <t>Página web con contenido</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8761256/</t>
+          <t>https://www.idexx.com/en/livestock/livestock-tests/poultry-tests/idexx-ai-multis-screen-ab-test/</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>PMC8761256</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>url:pmc.ncbi.nlm.nih.gov/articles/pmc8761256</t>
+          <t>url:idexx.com/en/livestock/livestock-tests/poultry-tests/idexx-ai-multis-screen-ab-test</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
@@ -5582,44 +5555,50 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Sin ruta</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Europe PMC no da el texto completo de PMC8761256 (sin licencia abierta) | solo hay la web de PMC, que no se usa (CAPTCHA); falta texto en Europe PMC</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>c) Web</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://www.idexx.com/en/livestock/livestock-tests/poultry-tests/idexx-ai-multis-screen-ab-test/</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Avian Influenza (AI) MultiS-Screen Ab Test - IDEXX US</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>75</v>
+      </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Limited detection of antibodies to clade 2.3.4.4 A/goose/Guangdong/1/1996 lineage HPAI virus in North American waterfowl</t>
+          <t>IDEXX AI MultiS-Screen Ab Test - pagina de producto</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Journal of Wildlife Diseases</t>
+          <t>IDEXX</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>s.f.</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
@@ -5631,7 +5610,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>D22</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5651,7 +5630,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Instructivo Tecnico para el Diagnostico de Influenza Aviar mediante ELISA y RT-PCR en tiempo real (D-ATR-AAT-013, version 03)</t>
+          <t>Limited detection of antibodies to clade 2.3.4.4 A/goose/Guangdong/1/1996 lineage HPAI virus in North American waterfowl</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5666,19 +5645,23 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>PDF directo</t>
+          <t>Artículo (web abierta)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-013%20IT%20Diagnostico%20Influenza%20Aviar.pdf</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC8761256/</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>PMC8761256</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/sites/default/files/d-atr-aat-013%20it%20diagnostico%20influenza%20aviar.pdf</t>
+          <t>url:pmc.ncbi.nlm.nih.gov/articles/pmc8761256</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5687,44 +5670,44 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>Sin ruta</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Europe PMC no da el texto completo de PMC8761256 (sin licencia abierta) | solo hay la web de PMC, que no se usa (CAPTCHA); falta texto en Europe PMC</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>d) PDF directo</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-013%20IT%20Diagnostico%20Influenza%20Aviar.pdf</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Instructivo Tecnico para el Diagnostico de Influenza Aviar mediante ELISA y RT-PCR en tiempo real (D-ATR-AAT-013, version 03)</t>
+          <t>Limited detection of antibodies to clade 2.3.4.4 A/goose/Guangdong/1/1996 lineage HPAI virus in North American waterfowl</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>SAG</t>
+          <t>Journal of Wildlife Diseases</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -5736,7 +5719,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D23</t>
+          <t>D22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5756,7 +5739,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Comparison of whole blood on filter strips with serum for avian influenza virus antibody detection in wild birds</t>
+          <t>Instructivo Tecnico para el Diagnostico de Influenza Aviar mediante ELISA y RT-PCR en tiempo real (D-ATR-AAT-013, version 03)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5771,52 +5754,28 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Artículo (web abierta)</t>
+          <t>PDF directo</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12146847/</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>10.1093/conphys/coaf033</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>PMC12146847</t>
-        </is>
-      </c>
+          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-013%20IT%20Diagnostico%20Influenza%20Aviar.pdf</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>doi:10.1093/conphys/coaf033</t>
+          <t>url:sag.gob.cl/sites/default/files/d-atr-aat-013%20it%20diagnostico%20influenza%20aviar.pdf</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1093/conphys/coaf033</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
           <t>OK</t>
@@ -5831,29 +5790,29 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>a) Europe PMC</t>
+          <t>d) PDF directo</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12146847/fullTextXML</t>
+          <t>https://www.sag.gob.cl/sites/default/files/D-ATR-AAT-013%20IT%20Diagnostico%20Influenza%20Aviar.pdf</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Comparison of whole blood on filter strips with serum for avian influenza virus antibody detection in wild birds</t>
+          <t>Instructivo Tecnico para el Diagnostico de Influenza Aviar mediante ELISA y RT-PCR en tiempo real (D-ATR-AAT-013, version 03)</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Conservation Physiology</t>
+          <t>SAG</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -5865,7 +5824,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>D24</t>
+          <t>D23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5885,7 +5844,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Surveillance of live birds for active and past infections reveals the impact of highly pathogenic H5N1 on seabird populations in Atlantic Canada</t>
+          <t>Comparison of whole blood on filter strips with serum for avian influenza virus antibody detection in wild birds</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5895,28 +5854,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Artículo (editorial)</t>
+          <t>Artículo (web abierta)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/org/science/article/pii/S0008416626000208</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC12146847/</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>10.1139/cjm-2025-0195</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>10.1093/conphys/coaf033</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>PMC12146847</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>doi:10.1139/cjm-2025-0195</t>
+          <t>doi:10.1093/conphys/coaf033</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -5933,48 +5896,52 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1139/cjm-2025-0195</t>
+          <t>https://doi.org/10.1093/conphys/coaf033</t>
         </is>
       </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Rechazado por la editorial</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>c) Web: cdnsciencepub.com rechaza el acceso (HTTP 403) | c) Web: www.sciencedirect.com rechaza bots (su robots.txt responde HTTP 403)</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr"/>
-      <c r="Y45" t="inlineStr"/>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>a) Europe PMC</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12146847/fullTextXML</t>
+        </is>
+      </c>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>Surveillance of live birds for active and past infections reveals the impact of highly pathogenic H5N1 on seabird populations in Atlantic Canada</t>
+          <t>Comparison of whole blood on filter strips with serum for avian influenza virus antibody detection in wild birds</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Canadian Journal of Microbiology</t>
+          <t>Conservation Physiology</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -5986,7 +5953,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6006,7 +5973,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Avian Sample Collection for Influenza A and Newcastle Disease (NVSL-WI-0023)</t>
+          <t>Surveillance of live birds for active and past infections reveals the impact of highly pathogenic H5N1 on seabird populations in Atlantic Canada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -6016,70 +5983,86 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>PDF directo</t>
+          <t>Artículo (editorial)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.aphis.usda.gov/sites/default/files/avian-sample-collection-ai-newcastle.pdf</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
+          <t>https://www.sciencedirect.com/org/science/article/pii/S0008416626000208</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>10.1139/cjm-2025-0195</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>url:aphis.usda.gov/sites/default/files/avian-sample-collection-ai-newcastle.pdf</t>
+          <t>doi:10.1139/cjm-2025-0195</t>
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1139/cjm-2025-0195</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>Rechazado por la editorial</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>c) Web: cdnsciencepub.com rechaza el acceso (HTTP 403) | c) Web: www.sciencedirect.com rechaza bots (su robots.txt responde HTTP 403)</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>d) PDF directo</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>https://www.aphis.usda.gov/sites/default/files/avian-sample-collection-ai-newcastle.pdf</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Avian Sample Collection for Influenza A and Newcastle Disease (NVSL-WI-0023)</t>
+          <t>Surveillance of live birds for active and past infections reveals the impact of highly pathogenic H5N1 on seabird populations in Atlantic Canada</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>USDA-APHIS NVSL</t>
+          <t>Canadian Journal of Microbiology</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
@@ -6091,7 +6074,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6111,67 +6094,43 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The MIQE Guidelines: Minimum Information for Publication of Quantitative Real-Time PCR Experiments</t>
+          <t>Avian Sample Collection for Influenza A and Newcastle Disease (NVSL-WI-0023)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>aviar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Artículo (DOI)</t>
+          <t>PDF directo</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1373/clinchem.2008.112797</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>10.1373/clinchem.2008.112797</t>
-        </is>
-      </c>
+          <t>https://www.aphis.usda.gov/sites/default/files/avian-sample-collection-ai-newcastle.pdf</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>doi:10.1373/clinchem.2008.112797</t>
+          <t>url:aphis.usda.gov/sites/default/files/avian-sample-collection-ai-newcastle.pdf</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>http://clinchem.aaccjnls.org/content/clinchem/55/4/611.full.pdf</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>http://clinchem.aaccjnls.org/content/clinchem/55/4/611.full.pdf</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
           <t>OK</t>
@@ -6186,41 +6145,41 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>b) PDF de OpenAlex</t>
+          <t>d) PDF directo</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>http://clinchem.aaccjnls.org/content/clinchem/55/4/611.full.pdf</t>
+          <t>https://www.aphis.usda.gov/sites/default/files/avian-sample-collection-ai-newcastle.pdf</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>The MIQE Guidelines: Minimum Information for Publication of Quantitative Real-Time PCR Experiments</t>
+          <t>Avian Sample Collection for Influenza A and Newcastle Disease (NVSL-WI-0023)</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Clinical Chemistry</t>
+          <t>USDA-APHIS NVSL</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>excel</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D32</t>
+          <t>D31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6240,7 +6199,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MIQE 2.0: Revision of the Minimum Information for Publication of Quantitative Real-Time PCR Experiments Guidelines</t>
+          <t>The MIQE Guidelines: Minimum Information for Publication of Quantitative Real-Time PCR Experiments</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6260,18 +6219,18 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/clinchem/hvaf043</t>
+          <t>https://doi.org/10.1373/clinchem.2008.112797</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>10.1093/clinchem/hvaf043</t>
+          <t>10.1373/clinchem.2008.112797</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>doi:10.1093/clinchem/hvaf043</t>
+          <t>doi:10.1373/clinchem.2008.112797</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -6288,12 +6247,12 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/clinchem/advance-article-pdf/doi/10.1093/clinchem/hvaf043/62999509/hvaf043.pdf</t>
+          <t>http://clinchem.aaccjnls.org/content/clinchem/55/4/611.full.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/clinchem/advance-article-pdf/doi/10.1093/clinchem/hvaf043/62999509/hvaf043.pdf</t>
+          <t>http://clinchem.aaccjnls.org/content/clinchem/55/4/611.full.pdf</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -6320,14 +6279,14 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/clinchem/advance-article-pdf/doi/10.1093/clinchem/hvaf043/62999509/hvaf043.pdf</t>
+          <t>http://clinchem.aaccjnls.org/content/clinchem/55/4/611.full.pdf</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>MIQE 2.0: Revision of the Minimum Information for Publication of Quantitative Real-Time PCR Experiments Guidelines</t>
+          <t>The MIQE Guidelines: Minimum Information for Publication of Quantitative Real-Time PCR Experiments</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6337,19 +6296,19 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>openalex</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D33</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6369,12 +6328,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Development of a real-time reverse transcriptase PCR assay for type A influenza virus and the avian H5 and H7 hemagglutinin subtypes</t>
+          <t>MIQE 2.0: Revision of the Minimum Information for Publication of Quantitative Real-Time PCR Experiments Guidelines</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>aviar</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -6389,18 +6348,18 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1128/JCM.40.9.3256-3260.2002</t>
+          <t>https://doi.org/10.1093/clinchem/hvaf043</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>10.1128/jcm.40.9.3256-3260.2002</t>
+          <t>10.1093/clinchem/hvaf043</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>doi:10.1128/jcm.40.9.3256-3260.2002</t>
+          <t>doi:10.1093/clinchem/hvaf043</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -6417,10 +6376,14 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/130722</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
+          <t>https://academic.oup.com/clinchem/advance-article-pdf/doi/10.1093/clinchem/hvaf043/62999509/hvaf043.pdf</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/clinchem/advance-article-pdf/doi/10.1093/clinchem/hvaf043/62999509/hvaf043.pdf</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr">
         <is>
           <t>no</t>
@@ -6428,37 +6391,41 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Sin ruta</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>solo hay la web de PMC, que no se usa (CAPTCHA); falta texto en Europe PMC</t>
-        </is>
-      </c>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr"/>
-      <c r="Y49" t="inlineStr"/>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>b) PDF de OpenAlex</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>https://academic.oup.com/clinchem/advance-article-pdf/doi/10.1093/clinchem/hvaf043/62999509/hvaf043.pdf</t>
+        </is>
+      </c>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>Development of a real-time reverse transcriptase PCR assay for type A influenza virus and the avian H5 and H7 hemagglutinin subtypes</t>
+          <t>MIQE 2.0: Revision of the Minimum Information for Publication of Quantitative Real-Time PCR Experiments Guidelines</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Journal of Clinical Microbiology</t>
+          <t>Clinical Chemistry</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -6470,7 +6437,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6480,94 +6447,108 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>bioseguridad</t>
+          <t>diagnostico</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ley 18.755 – Establece normas sobre el Servicio Agrícola y Ganadero (Ley Orgánica del SAG)</t>
+          <t>Development of a real-time reverse transcriptase PCR assay for type A influenza virus and the avian H5 and H7 hemagglutinin subtypes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>aviar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Página web con contenido</t>
+          <t>Artículo (DOI)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=30135</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+          <t>https://doi.org/10.1128/JCM.40.9.3256-3260.2002</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>10.1128/jcm.40.9.3256-3260.2002</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>url:bcn.cl/leychile/navegar?idnorma=30135</t>
+          <t>doi:10.1128/jcm.40.9.3256-3260.2002</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://www.ncbi.nlm.nih.gov/pmc/articles/130722</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Revisar título</t>
+          <t>Sin ruta</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>el &lt;title&gt; se parece 38/100 al título esperado</t>
+          <t>solo hay la web de PMC, que no se usa (CAPTCHA); falta texto en Europe PMC</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>c) Web</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>https://www.bcn.cl/leychile/Navegar/imprimir?idNorma=30135</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Ley Chile - Biblioteca del Congreso Nacional</t>
-        </is>
-      </c>
-      <c r="AA50" t="n">
-        <v>38</v>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Ley 18.755 – Establece normas sobre el Servicio Agrícola y Ganadero (Ley Orgánica del SAG)</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
+          <t>Development of a real-time reverse transcriptase PCR assay for type A influenza virus and the avian H5 and H7 hemagglutinin subtypes</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Journal of Clinical Microbiology</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
       <c r="AE50" t="inlineStr">
         <is>
           <t>excel</t>
@@ -6577,7 +6558,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6597,7 +6578,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Resolución Exenta N° 4.869 – Medidas sanitarias y obligaciones para terceros en contexto de enfermedades declaradas bajo control oficial</t>
+          <t>Ley 18.755 – Establece normas sobre el Servicio Agrícola y Ganadero (Ley Orgánica del SAG)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6617,14 +6598,14 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1224888</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=30135</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>url:bcn.cl/leychile/navegar?idnorma=1224888</t>
+          <t>url:bcn.cl/leychile/navegar?idnorma=30135</t>
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
@@ -6641,7 +6622,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>el &lt;title&gt; se parece 30/100 al título esperado</t>
+          <t>el &lt;title&gt; se parece 38/100 al título esperado</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -6657,7 +6638,7 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/Navegar/imprimir?idNorma=1224888</t>
+          <t>https://www.bcn.cl/leychile/Navegar/imprimir?idNorma=30135</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
@@ -6666,11 +6647,11 @@
         </is>
       </c>
       <c r="AA51" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Resolución Exenta N° 4.869 – Medidas sanitarias y obligaciones para terceros en contexto de enfermedades declaradas bajo control oficial</t>
+          <t>Ley 18.755 – Establece normas sobre el Servicio Agrícola y Ganadero (Ley Orgánica del SAG)</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -6684,7 +6665,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6704,7 +6685,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Resolución Exenta N° 7.192/2022 – Declara emergencia zoosanitaria y activa el Sistema Nacional de Emergencia del SAG</t>
+          <t>Resolución Exenta N° 4.869 – Medidas sanitarias y obligaciones para terceros en contexto de enfermedades declaradas bajo control oficial</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6719,19 +6700,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>PDF directo</t>
+          <t>Página web con contenido</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/RESOLUCI%C3%93N%20EXENTA%20N%C2%BA%2071922022_Declara%20emergencia%20y%20activa%20comit%C3%A9.pdf</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1224888</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/sites/default/files/resoluci%c3%93n%20exenta%20n%c2%ba%2071922022_declara%20emergencia%20y%20activa%20comit%c3%a9.pdf</t>
+          <t>url:bcn.cl/leychile/navegar?idnorma=1224888</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -6743,10 +6724,14 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr"/>
+          <t>Revisar título</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>el &lt;title&gt; se parece 30/100 al título esperado</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
@@ -6755,19 +6740,25 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>d) PDF directo</t>
+          <t>c) Web</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/RESOLUCI%C3%93N%20EXENTA%20N%C2%BA%2071922022_Declara%20emergencia%20y%20activa%20comit%C3%A9.pdf</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
+          <t>https://www.bcn.cl/leychile/Navegar/imprimir?idNorma=1224888</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Ley Chile - Biblioteca del Congreso Nacional</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>30</v>
+      </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Resolución Exenta N° 7.192/2022 – Declara emergencia zoosanitaria y activa el Sistema Nacional de Emergencia del SAG</t>
+          <t>Resolución Exenta N° 4.869 – Medidas sanitarias y obligaciones para terceros en contexto de enfermedades declaradas bajo control oficial</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -6781,7 +6772,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6801,12 +6792,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Instructivo Técnico – Bioseguridad de las Personas en una Emergencia Zoosanitaria con Riesgo de Zoonosis: Influenza Aviar (IA)</t>
+          <t>Resolución Exenta N° 7.192/2022 – Declara emergencia zoosanitaria y activa el Sistema Nacional de Emergencia del SAG</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>aviar</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -6821,14 +6812,14 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/IT-Bioseguridad-Influenza-Aviar_junio_26_V3.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/RESOLUCI%C3%93N%20EXENTA%20N%C2%BA%2071922022_Declara%20emergencia%20y%20activa%20comit%C3%A9.pdf</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/sites/default/files/it-bioseguridad-influenza-aviar_junio_26_v3.pdf</t>
+          <t>url:sag.gob.cl/sites/default/files/resoluci%c3%93n%20exenta%20n%c2%ba%2071922022_declara%20emergencia%20y%20activa%20comit%c3%a9.pdf</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -6857,14 +6848,14 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/IT-Bioseguridad-Influenza-Aviar_junio_26_V3.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/RESOLUCI%C3%93N%20EXENTA%20N%C2%BA%2071922022_Declara%20emergencia%20y%20activa%20comit%C3%A9.pdf</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Instructivo Técnico – Bioseguridad de las Personas en una Emergencia Zoosanitaria con Riesgo de Zoonosis: Influenza Aviar (IA)</t>
+          <t>Resolución Exenta N° 7.192/2022 – Declara emergencia zoosanitaria y activa el Sistema Nacional de Emergencia del SAG</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -6878,7 +6869,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>E7</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6898,7 +6889,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Procedimiento P-PP-VE-006 – Contingencia de Influenza Aviar</t>
+          <t>Instructivo Técnico – Bioseguridad de las Personas en una Emergencia Zoosanitaria con Riesgo de Zoonosis: Influenza Aviar (IA)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6918,14 +6909,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/esp/Animal_Health_in_the_World/docs/pdf/pagAtachadorVisualizador_1.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/IT-Bioseguridad-Influenza-Aviar_junio_26_V3.pdf</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>url:woah.org/fileadmin/home/esp/animal_health_in_the_world/docs/pdf/pagatachadorvisualizador_1.pdf</t>
+          <t>url:sag.gob.cl/sites/default/files/it-bioseguridad-influenza-aviar_junio_26_v3.pdf</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -6954,14 +6945,14 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/esp/Animal_Health_in_the_World/docs/pdf/pagAtachadorVisualizador_1.pdf</t>
+          <t>https://www.sag.gob.cl/sites/default/files/IT-Bioseguridad-Influenza-Aviar_junio_26_V3.pdf</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Procedimiento P-PP-VE-006 – Contingencia de Influenza Aviar</t>
+          <t>Instructivo Técnico – Bioseguridad de las Personas en una Emergencia Zoosanitaria con Riesgo de Zoonosis: Influenza Aviar (IA)</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -6975,7 +6966,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>E10</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6995,7 +6986,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brote Influenza aviar 2026. Antecedentes generales y situación nacional (Asesoría Técnica Parlamentaria)</t>
+          <t>Procedimiento P-PP-VE-006 – Contingencia de Influenza Aviar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7010,19 +7001,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Página web con contenido</t>
+          <t>PDF directo</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/asesoriasparlamentarias/detalle_documento.html?id=85550</t>
+          <t>https://www.woah.org/fileadmin/Home/esp/Animal_Health_in_the_World/docs/pdf/pagAtachadorVisualizador_1.pdf</t>
         </is>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>url:bcn.cl/asesoriasparlamentarias/detalle_documento.html?id=85550</t>
+          <t>url:woah.org/fileadmin/home/esp/animal_health_in_the_world/docs/pdf/pagatachadorvisualizador_1.pdf</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -7046,29 +7037,31 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>c) Web</t>
+          <t>d) PDF directo</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/asesoriasparlamentarias/detalle_documento.html?id=85550</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Brote Influenza aviar 2026. Antecedentes generales y situación nacional. Detalle Dcumento. Asesorías Parlamentarias | Biblioteca del Congreso Nacional de Chile 111</t>
-        </is>
-      </c>
-      <c r="AA55" t="n">
-        <v>81</v>
-      </c>
+          <t>https://www.woah.org/fileadmin/Home/esp/Animal_Health_in_the_World/docs/pdf/pagAtachadorVisualizador_1.pdf</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Brote Influenza aviar 2026. Antecedentes generales y situación nacional (Asesoría Técnica Parlamentaria)</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
+          <t>Procedimiento P-PP-VE-006 – Contingencia de Influenza Aviar</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>SAG</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
       <c r="AE55" t="inlineStr">
         <is>
           <t>excel</t>
@@ -7078,7 +7071,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7098,12 +7091,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SAG – Pecuaria (ámbito de acción)</t>
+          <t>Brote Influenza aviar 2026. Antecedentes generales y situación nacional (Asesoría Técnica Parlamentaria)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>aviar</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -7118,14 +7111,14 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/ambitos-de-accion/pecuaria</t>
+          <t>https://www.bcn.cl/asesoriasparlamentarias/detalle_documento.html?id=85550</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/ambitos-de-accion/pecuaria</t>
+          <t>url:bcn.cl/asesoriasparlamentarias/detalle_documento.html?id=85550</t>
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
@@ -7154,20 +7147,20 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/ambitos-de-accion/pecuaria</t>
+          <t>https://www.bcn.cl/asesoriasparlamentarias/detalle_documento.html?id=85550</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>Pecuaria | SAG</t>
+          <t>Brote Influenza aviar 2026. Antecedentes generales y situación nacional. Detalle Dcumento. Asesorías Parlamentarias | Biblioteca del Congreso Nacional de Chile 111</t>
         </is>
       </c>
       <c r="AA56" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>SAG – Pecuaria (ámbito de acción)</t>
+          <t>Brote Influenza aviar 2026. Antecedentes generales y situación nacional (Asesoría Técnica Parlamentaria)</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -7181,7 +7174,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7201,7 +7194,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SAG – Situación sanitaria nacional</t>
+          <t>SAG – Pecuaria (ámbito de acción)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7221,14 +7214,14 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/ambitos-de-accion/situacion-sanitaria-nacional</t>
+          <t>https://www.sag.gob.cl/ambitos-de-accion/pecuaria</t>
         </is>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/ambitos-de-accion/situacion-sanitaria-nacional</t>
+          <t>url:sag.gob.cl/ambitos-de-accion/pecuaria</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -7257,12 +7250,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/ambitos-de-accion/situacion-sanitaria-nacional</t>
+          <t>https://www.sag.gob.cl/ambitos-de-accion/pecuaria</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>Situación sanitaria nacional | SAG</t>
+          <t>Pecuaria | SAG</t>
         </is>
       </c>
       <c r="AA57" t="n">
@@ -7270,7 +7263,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>SAG – Situación sanitaria nacional</t>
+          <t>SAG – Pecuaria (ámbito de acción)</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -7284,7 +7277,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>E19</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7304,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SAG – Resolución Exenta N° 7.050: aprueba Instructivo Técnico de Bioseguridad de las Personas (influenza aviar), versión 3</t>
+          <t>SAG – Situación sanitaria nacional</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>aviar</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -7324,14 +7317,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/content/aprueba-instructivo-tecnico-de-bioseguridad-de-las-personas-en-una-emergencia-zoosanitaria-con-riesgo-de-zoonosis-influenza-aviar-ia-version-3-y-dejese-sin-efecto-la-resolucion-exenta-ndeg-39962026</t>
+          <t>https://www.sag.gob.cl/ambitos-de-accion/situacion-sanitaria-nacional</t>
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/content/aprueba-instructivo-tecnico-de-bioseguridad-de-las-personas-en-una-emergencia-zoosanitaria-con-riesgo-de-zoonosis-influenza-aviar-ia-version-3-y-dejese-sin-efecto-la-resolucion-exenta-ndeg-39962026</t>
+          <t>url:sag.gob.cl/ambitos-de-accion/situacion-sanitaria-nacional</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -7360,20 +7353,20 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/content/aprueba-instructivo-tecnico-de-bioseguridad-de-las-personas-en-una-emergencia-zoosanitaria-con-riesgo-de-zoonosis-influenza-aviar-ia-version-3-y-dejese-sin-efecto-la-resolucion-exenta-ndeg-39962026</t>
+          <t>https://www.sag.gob.cl/ambitos-de-accion/situacion-sanitaria-nacional</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Aprueba instructivo técnico de bioseguridad de las personas en una emergencia zoosanitaria con riesgo de zoonosis, influenza aviar (IA) versión 3 y déjese sin efecto la Resolución Exenta N° 3996/2026 | SAG</t>
+          <t>Situación sanitaria nacional | SAG</t>
         </is>
       </c>
       <c r="AA58" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>SAG – Resolución Exenta N° 7.050: aprueba Instructivo Técnico de Bioseguridad de las Personas (influenza aviar), versión 3</t>
+          <t>SAG – Situación sanitaria nacional</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -7387,7 +7380,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>E20</t>
+          <t>E19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7407,12 +7400,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FAO – Comunicadores del SAG participan de taller de la FAO en comunicación de riesgos en el marco de Una Salud</t>
+          <t>SAG – Resolución Exenta N° 7.050: aprueba Instructivo Técnico de Bioseguridad de las Personas (influenza aviar), versión 3</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>aviar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -7427,14 +7420,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.fao.org/chile/news-and-opinion/news/detail/comunicadores-del-sag-participan-de-taller-de-la-fao-en-comunicaci%C3%B3n-de-riesgos-en-el-marco-de-una-salud/es</t>
+          <t>https://www.sag.gob.cl/content/aprueba-instructivo-tecnico-de-bioseguridad-de-las-personas-en-una-emergencia-zoosanitaria-con-riesgo-de-zoonosis-influenza-aviar-ia-version-3-y-dejese-sin-efecto-la-resolucion-exenta-ndeg-39962026</t>
         </is>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>url:fao.org/chile/news-and-opinion/news/detail/comunicadores-del-sag-participan-de-taller-de-la-fao-en-comunicaci%c3%b3n-de-riesgos-en-el-marco-de-una-salud/es</t>
+          <t>url:sag.gob.cl/content/aprueba-instructivo-tecnico-de-bioseguridad-de-las-personas-en-una-emergencia-zoosanitaria-con-riesgo-de-zoonosis-influenza-aviar-ia-version-3-y-dejese-sin-efecto-la-resolucion-exenta-ndeg-39962026</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
@@ -7463,20 +7456,20 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>https://www.fao.org/chile/news-and-opinion/news/detail/comunicadores-del-sag-participan-de-taller-de-la-fao-en-comunicaci%C3%B3n-de-riesgos-en-el-marco-de-una-salud/es</t>
+          <t>https://www.sag.gob.cl/content/aprueba-instructivo-tecnico-de-bioseguridad-de-las-personas-en-una-emergencia-zoosanitaria-con-riesgo-de-zoonosis-influenza-aviar-ia-version-3-y-dejese-sin-efecto-la-resolucion-exenta-ndeg-39962026</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>Comunicadores del SAG participan de taller de la FAO en comunicación de riesgos en el marco de Una Salud</t>
+          <t>Aprueba instructivo técnico de bioseguridad de las personas en una emergencia zoosanitaria con riesgo de zoonosis, influenza aviar (IA) versión 3 y déjese sin efecto la Resolución Exenta N° 3996/2026 | SAG</t>
         </is>
       </c>
       <c r="AA59" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>FAO – Comunicadores del SAG participan de taller de la FAO en comunicación de riesgos en el marco de Una Salud</t>
+          <t>SAG – Resolución Exenta N° 7.050: aprueba Instructivo Técnico de Bioseguridad de las Personas (influenza aviar), versión 3</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -7490,7 +7483,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E21</t>
+          <t>E20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7510,7 +7503,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FAO – EMPRES-i (página 'Acerca de' del sitio data.apps.fao.org)</t>
+          <t>FAO – Comunicadores del SAG participan de taller de la FAO en comunicación de riesgos en el marco de Una Salud</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7530,14 +7523,14 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://data.apps.fao.org/static/sites/empres-i/about.html</t>
+          <t>https://www.fao.org/chile/news-and-opinion/news/detail/comunicadores-del-sag-participan-de-taller-de-la-fao-en-comunicaci%C3%B3n-de-riesgos-en-el-marco-de-una-salud/es</t>
         </is>
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>url:data.apps.fao.org/static/sites/empres-i/about.html</t>
+          <t>url:fao.org/chile/news-and-opinion/news/detail/comunicadores-del-sag-participan-de-taller-de-la-fao-en-comunicaci%c3%b3n-de-riesgos-en-el-marco-de-una-salud/es</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
@@ -7566,20 +7559,20 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>https://data.apps.fao.org/static/sites/empres-i/about.html</t>
+          <t>https://www.fao.org/chile/news-and-opinion/news/detail/comunicadores-del-sag-participan-de-taller-de-la-fao-en-comunicaci%C3%B3n-de-riesgos-en-el-marco-de-una-salud/es</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>FAO EMPRES-i - About</t>
+          <t>Comunicadores del SAG participan de taller de la FAO en comunicación de riesgos en el marco de Una Salud</t>
         </is>
       </c>
       <c r="AA60" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>FAO – EMPRES-i (página 'Acerca de' del sitio data.apps.fao.org)</t>
+          <t>FAO – Comunicadores del SAG participan de taller de la FAO en comunicación de riesgos en el marco de Una Salud</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -7593,7 +7586,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>E22</t>
+          <t>E21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7613,7 +7606,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FAO y SAG fortalecen capacidades para la evaluación rápida de riesgos con enfoque Una Salud</t>
+          <t>FAO – EMPRES-i (página 'Acerca de' del sitio data.apps.fao.org)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7633,14 +7626,14 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.fao.org/chile/news-and-opinion/news/detail/fao-y-sag-fortalecen-capacidades-para-la-evaluaci%C3%B3n-r%C3%A1pida-de-riesgos-con-enfoque-una-salud/es</t>
+          <t>https://data.apps.fao.org/static/sites/empres-i/about.html</t>
         </is>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>url:fao.org/chile/news-and-opinion/news/detail/fao-y-sag-fortalecen-capacidades-para-la-evaluaci%c3%b3n-r%c3%a1pida-de-riesgos-con-enfoque-una-salud/es</t>
+          <t>url:data.apps.fao.org/static/sites/empres-i/about.html</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -7669,20 +7662,20 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>https://www.fao.org/chile/news-and-opinion/news/detail/fao-y-sag-fortalecen-capacidades-para-la-evaluaci%C3%B3n-r%C3%A1pida-de-riesgos-con-enfoque-una-salud/es</t>
+          <t>https://data.apps.fao.org/static/sites/empres-i/about.html</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>FAO y SAG fortalecen capacidades para la evaluación rápida de riesgos con enfoque Una Salud</t>
+          <t>FAO EMPRES-i - About</t>
         </is>
       </c>
       <c r="AA61" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>FAO y SAG fortalecen capacidades para la evaluación rápida de riesgos con enfoque Una Salud</t>
+          <t>FAO – EMPRES-i (página 'Acerca de' del sitio data.apps.fao.org)</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -7696,7 +7689,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>E23</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7716,7 +7709,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FAO – Preguntas frecuentes sobre EMA-i+ y EMPRES-i+</t>
+          <t>FAO y SAG fortalecen capacidades para la evaluación rápida de riesgos con enfoque Una Salud</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7736,14 +7729,14 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.fao.org/animal-health/resources/tools/faq-ema-i-empres-i/en</t>
+          <t>https://www.fao.org/chile/news-and-opinion/news/detail/fao-y-sag-fortalecen-capacidades-para-la-evaluaci%C3%B3n-r%C3%A1pida-de-riesgos-con-enfoque-una-salud/es</t>
         </is>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>url:fao.org/animal-health/resources/tools/faq-ema-i-empres-i/en</t>
+          <t>url:fao.org/chile/news-and-opinion/news/detail/fao-y-sag-fortalecen-capacidades-para-la-evaluaci%c3%b3n-r%c3%a1pida-de-riesgos-con-enfoque-una-salud/es</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -7772,20 +7765,20 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>https://www.fao.org/animal-health/resources/tools/faq-ema-i-empres-i/en</t>
+          <t>https://www.fao.org/chile/news-and-opinion/news/detail/fao-y-sag-fortalecen-capacidades-para-la-evaluaci%C3%B3n-r%C3%A1pida-de-riesgos-con-enfoque-una-salud/es</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>FAQ on EMA-i+ and EMPRES-i+</t>
+          <t>FAO y SAG fortalecen capacidades para la evaluación rápida de riesgos con enfoque Una Salud</t>
         </is>
       </c>
       <c r="AA62" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>FAO – Preguntas frecuentes sobre EMA-i+ y EMPRES-i+</t>
+          <t>FAO y SAG fortalecen capacidades para la evaluación rápida de riesgos con enfoque Una Salud</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -7799,7 +7792,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7819,7 +7812,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FAO – EMPRES-i (proyecto en AgroInformática)</t>
+          <t>FAO – Preguntas frecuentes sobre EMA-i+ y EMPRES-i+</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7839,14 +7832,14 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.fao.org/agroinformatics/projects/projects-detail/empres-i/</t>
+          <t>https://www.fao.org/animal-health/resources/tools/faq-ema-i-empres-i/en</t>
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>url:fao.org/agroinformatics/projects/projects-detail/empres-i</t>
+          <t>url:fao.org/animal-health/resources/tools/faq-ema-i-empres-i/en</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
@@ -7875,20 +7868,20 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>https://www.fao.org/agroinformatics/projects/projects-detail/empres-i/</t>
+          <t>https://www.fao.org/animal-health/resources/tools/faq-ema-i-empres-i/en</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>EMPRES-i</t>
+          <t>FAQ on EMA-i+ and EMPRES-i+</t>
         </is>
       </c>
       <c r="AA63" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>FAO – EMPRES-i (proyecto en AgroInformática)</t>
+          <t>FAO – Preguntas frecuentes sobre EMA-i+ y EMPRES-i+</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -7902,7 +7895,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7912,7 +7905,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eje F</t>
+          <t>Eje E</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7922,12 +7915,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PLAN DE CONTINGENCIA VERSIÓN 6.0 Influenza Aviar</t>
+          <t>FAO – EMPRES-i (proyecto en AgroInformática)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>aviar</t>
+          <t>general</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -7937,19 +7930,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>PDF directo</t>
+          <t>Página web con contenido</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/Plan%20de%20Contingencia%20Chile%20Actualizado%20V.6.pdf</t>
+          <t>https://www.fao.org/agroinformatics/projects/projects-detail/empres-i/</t>
         </is>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>url:sag.gob.cl/sites/default/files/plan%20de%20contingencia%20chile%20actualizado%20v.6.pdf</t>
+          <t>url:fao.org/agroinformatics/projects/projects-detail/empres-i</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -7973,19 +7966,25 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>d) PDF directo</t>
+          <t>c) Web</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/Plan%20de%20Contingencia%20Chile%20Actualizado%20V.6.pdf</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
+          <t>https://www.fao.org/agroinformatics/projects/projects-detail/empres-i/</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>EMPRES-i</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>100</v>
+      </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>PLAN DE CONTINGENCIA VERSIÓN 6.0 Influenza Aviar</t>
+          <t>FAO – EMPRES-i (proyecto en AgroInformática)</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -8019,7 +8018,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>INFORME EPIDEMIOLÓGICO: Vigilancia de expuestos a influenza aviar</t>
+          <t>Informe epidemiológico: Vigilancia de expuestos a influenza aviar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -8082,7 +8081,7 @@
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>INFORME EPIDEMIOLÓGICO: Vigilancia de expuestos a influenza aviar</t>
+          <t>Informe epidemiológico: Vigilancia de expuestos a influenza aviar</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -8116,7 +8115,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PROTOCOLO DE VIGILANCIA OCUPACIONAL POR EXPOSICIÓN A INFLUENZA AVIAR Versión Nº2</t>
+          <t>Protocolo de vigilancia ocupacional por exposición a influenza aviar, versión 2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -8179,7 +8178,7 @@
       <c r="AA66" t="inlineStr"/>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>PROTOCOLO DE VIGILANCIA OCUPACIONAL POR EXPOSICIÓN A INFLUENZA AVIAR Versión Nº2</t>
+          <t>Protocolo de vigilancia ocupacional por exposición a influenza aviar, versión 2</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -17145,85 +17144,61 @@
           <t>10.1371/journal.pone.0319880</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>PMC12412978</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>doi:10.1371/journal.pone.0319880</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>https://journals.plos.org/plosone/article/file?id=10.1371/journal.pone.0319880&amp;type=printable</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>https://journals.plos.org/plosone/article/file?id=10.1371/journal.pone.0319880&amp;type=printable</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr"/>
+          <t>Duplicado</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>mismo DOI/URL que A3</t>
+        </is>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" t="inlineStr">
         <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>a) Europe PMC</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>https://www.ebi.ac.uk/europepmc/webservices/rest/PMC12412978/fullTextXML</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr"/>
+      <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr"/>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>Genetic data and meteorological conditions suggesting windborne transmission of H5N1 high-pathogenicity avian influenza between commercial poultry outbreaks</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>PLoS ONE</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+          <t>Genetic data and meteorological conditions suggesting windborne transmission of H5N1 high-pathogenicity avian influenza between commercial poultry outbreaks.</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>excel</t>
         </is>
       </c>
     </row>
@@ -43358,7 +43333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43438,7 +43413,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -43453,29 +43428,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Inactivation of the infectivity of two highly pathogenic avian influenza viruses and a virulent Newcastle disease virus by ultraviolet radiation</t>
+          <t>Immunoglobulins in piglets from sows heat-stressed prepartum</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1080/03079457.2013.853867</t>
+          <t>https://doi.org/10.2527/jas1987.652445x</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -43490,29 +43465,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Inactivation of the novel avian influenza A (H7N9) virus under physical conditions or chemical agents treatment</t>
+          <t>The effect of heat stress on intestinal integrity and Salmonella invasion in broiler birds</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://virologyj.biomedcentral.com/articles/10.1186/1743-422X-10-289</t>
+          <t>https://doi.org/10.1016/j.jtherbio.2017.10.015</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -43527,29 +43502,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Immunoglobulins in piglets from sows heat-stressed prepartum</t>
+          <t>Servicios Climaticos - Direccion Meteorologica de Chile</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2527/jas1987.652445x</t>
+          <t>https://climatologia.meteochile.gob.cl/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -43564,29 +43539,29 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The effect of heat stress on intestinal integrity and Salmonella invasion in broiler birds</t>
+          <t>Ficha Tecnica: Sindrome Reproductivo y Respiratorio Porcino (PRRS), Version 01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jtherbio.2017.10.015</t>
+          <t>http://www.sag.cl/sites/default/files/plan_oficial_control_erradicac_prrs_vs_2_junio-2014.pdf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -43601,29 +43576,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Servicios Climaticos - Direccion Meteorologica de Chile</t>
+          <t>Ficha de evaluacion ex post: Programa Nacional de Diagnostico, Control, Eliminacion y Erradicacion del PRRS de los planteles porcinos (Proyecto 41-14-200)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://climatologia.meteochile.gob.cl/</t>
+          <t>https://www.sag.gob.cl/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -43638,12 +43613,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ficha Tecnica: Sindrome Reproductivo y Respiratorio Porcino (PRRS), Version 01</t>
+          <t>Use of a production region model to assess the airborne spread of porcine reproductive and respiratory syndrome virus</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>http://www.sag.cl/sites/default/files/plan_oficial_control_erradicac_prrs_vs_2_junio-2014.pdf</t>
+          <t>https://doi.org/10.1016/j.vetmic.2008.10.013</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -43660,7 +43635,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -43675,12 +43650,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ficha de evaluacion ex post: Programa Nacional de Diagnostico, Control, Eliminacion y Erradicacion del PRRS de los planteles porcinos (Proyecto 41-14-200)</t>
+          <t>Effect of temperature and relative humidity on the stability of infectious porcine reproductive and respiratory syndrome virus in aerosols</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/</t>
+          <t>https://doi.org/10.1051/vetres:2006044</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -43697,7 +43672,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -43712,12 +43687,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Use of a production region model to assess the airborne spread of porcine reproductive and respiratory syndrome virus</t>
+          <t>Mitigation of airborne PRRSV transmission with UV light treatment: proof-of-concept</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.vetmic.2008.10.013</t>
+          <t>https://doi.org/10.3390/agriculture11030259</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -43734,7 +43709,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -43749,12 +43724,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Effect of temperature and relative humidity on the stability of infectious porcine reproductive and respiratory syndrome virus in aerosols</t>
+          <t>Assessment of temperature and time on the survivability of porcine reproductive and respiratory syndrome virus (PRRSV) and porcine epidemic diarrhea virus (PEDV) on experimentally contaminated surfaces</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1051/vetres:2006044</t>
+          <t>https://doi.org/10.1371/journal.pone.0291181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -43771,7 +43746,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -43786,29 +43761,29 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mitigation of airborne PRRSV transmission with UV light treatment: proof-of-concept</t>
+          <t>Decreto con Fuerza de Ley R.R.A. N 16: Sobre Sanidad y Proteccion Animal</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/agriculture11030259</t>
+          <t>https://www.bcn.cl/leychile</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -43823,12 +43798,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assessment of temperature and time on the survivability of porcine reproductive and respiratory syndrome virus (PRRSV) and porcine epidemic diarrhea virus (PEDV) on experimentally contaminated surfaces</t>
+          <t>Decreto Supremo N 235: Aprueba reglamento para la erradicacion del sindrome disgenesico y respiratorio del cerdo o PRRS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1371/journal.pone.0291181</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=194922</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -43845,7 +43820,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -43860,29 +43835,29 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Decreto con Fuerza de Ley R.R.A. N 16: Sobre Sanidad y Proteccion Animal</t>
+          <t>Decreto Exento N 389: Actualiza lista de enfermedades de declaracion obligatoria para la aplicacion de medidas sanitarias</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1070774</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -43897,29 +43872,29 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Decreto Supremo N 235: Aprueba reglamento para la erradicacion del sindrome disgenesico y respiratorio del cerdo o PRRS</t>
+          <t>Resolucion Exenta N 4.887: Crea el programa de bioseguridad para establecimientos pecuarios industriales y fija sus exigencias</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile</t>
+          <t>https://www.sag.gob.cl/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -43934,29 +43909,29 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Decreto Exento N 389: Actualiza lista de enfermedades de declaracion obligatoria para la aplicacion de medidas sanitarias</t>
+          <t>Resolucion Exenta N 2.344: Fija exigencias sanitarias para la movilizacion e internacion de porcinos reproductores en el territorio nacional</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile</t>
+          <t>https://www.sag.gob.cl/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -43971,29 +43946,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Resolucion Exenta N 4.887: Crea el programa de bioseguridad para establecimientos pecuarios industriales y fija sus exigencias</t>
+          <t>Resolucion Exenta N 2.113: Declara pais libre del virus del Sindrome Reproductivo y Respiratorio Porcino (PRRS)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1202659</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -44008,12 +43983,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Resolucion Exenta N 2.344: Fija exigencias sanitarias para la movilizacion e internacion de porcinos reproductores en el territorio nacional</t>
+          <t>Aerosol detection and transmission of porcine reproductive and respiratory syndrome virus (PRRSV): what is the evidence, and what are the knowledge gaps?</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/</t>
+          <t>https://doi.org/10.3390/v11080712</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -44030,7 +44005,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -44040,34 +44015,34 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eje A</t>
+          <t>Eje B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Resolucion Exenta N 2.113: Declara pais libre del virus del Sindrome Reproductivo y Respiratorio Porcino (PRRS)</t>
+          <t>Estudio de la excreción y transmisión del aislado chileno del virus del síndrome respiratorio y reproductivo porcino (PRRS) en animales inoculados experimentalmente y centinelas en contacto mediante RT-nPCR y ELISA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.diariooficial.interior.gob.cl/publicaciones/2024/04/16/43827/01/2479246.pdf</t>
+          <t>https://www.scielo.cl/scielo.php?pid=S0301-732X2009000300006&amp;script=sci_arttext</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -44077,17 +44052,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eje A</t>
+          <t>Eje B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Aerosol detection and transmission of porcine reproductive and respiratory syndrome virus (PRRSV): what is the evidence, and what are the knowledge gaps?</t>
+          <t>DETECCIÓN DE VIRUS DEL SÍNDROME REPRODUCTIVO Y RESPIRATORIO PORCINO (PRRS) EN FÓMITES, VECTORES Y AIRE EN DOS GRANJAS INTENSIVAS DE CERDOS DE LA REGIÓN METROPOLITANA DE CHILE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/v11080712</t>
+          <t>https://repositorio.uchile.cl/bitstream/handle/2250/196959/Detecci%C3%B3n-de-virus-del-s%C3%ADndrome-reproductivo-y-respiratorio-porcino-(prrs)-en-f%C3%B3mites%2C-vectores-y-aire-en-dos-granjas.pdf?sequence=1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -44104,7 +44079,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -44119,12 +44094,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Estudio de la excreción y transmisión del aislado chileno del virus del síndrome respiratorio y reproductivo porcino (PRRS) en animales inoculados experimentalmente y centinelas en contacto mediante RT-nPCR y ELISA</t>
+          <t>Autodeclaración de Chile como país libre de infección por el virus del Síndrome Reproductivo y Respiratorio Porcino</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.scielo.cl/scielo.php?pid=S0301-732X2009000300006&amp;script=sci_arttext</t>
+          <t>https://www.woah.org/app/uploads/2024/10/2024-10-chile-prrs-selfd-esp.pdf</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -44141,7 +44116,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -44156,12 +44131,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DETECCIÓN DE VIRUS DEL SÍNDROME REPRODUCTIVO Y RESPIRATORIO PORCINO (PRRS) EN FÓMITES, VECTORES Y AIRE EN DOS GRANJAS INTENSIVAS DE CERDOS DE LA REGIÓN METROPOLITANA DE CHILE</t>
+          <t>Plan Anual de Vigilancia de Enfermedades Exóticas 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://repositorio.uchile.cl/bitstream/handle/2250/196959/Detecci%C3%B3n-de-virus-del-s%C3%ADndrome-reproductivo-y-respiratorio-porcino-(prrs)-en-f%C3%B3mites%2C-vectores-y-aire-en-dos-granjas.pdf?sequence=1</t>
+          <t>https://www.sag.cl/sites/default/files/Plan%20Anual%20de%20Vigilancia%20de%20Enfermedades%20Ex%C3%B3ticas%20a%C3%B1o%202026%20Versi%C3%B3n%201%201.pdf</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -44178,7 +44153,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -44193,12 +44168,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Autodeclaración de Chile como país libre de infección por el virus del Síndrome Reproductivo y Respiratorio Porcino</t>
+          <t>Resolución 8057 Exenta (30-NOV-2024)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.woah.org/app/uploads/2024/10/2024-10-chile-prrs-selfd-esp.pdf</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1208816</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -44215,7 +44190,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -44230,12 +44205,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Plan Anual de Vigilancia de Enfermedades Exóticas 2026</t>
+          <t>Epidemiological investigations of the introduction of PRRSV in Chile, 2013–2015</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.sag.cl/sites/default/files/Plan%20Anual%20de%20Vigilancia%20de%20Enfermedades%20Ex%C3%B3ticas%20a%C3%B1o%202026%20Versi%C3%B3n%201%201.pdf</t>
+          <t>https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0181569</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -44252,7 +44227,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>B7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -44267,12 +44242,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Resolución 8057 Exenta (30-NOV-2024)</t>
+          <t>Características hematológicas y patológicas de cerdos inoculados experimentalmente con el aislado chileno del virus síndrome respiratorio y reproductivo porcino</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1208816</t>
+          <t>https://www.scielo.cl/scielo.php?script=sci_arttext&amp;pid=S0301-732X2006000200009</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -44289,7 +44264,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -44304,12 +44279,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Epidemiological investigations of the introduction of PRRSV in Chile, 2013–2015</t>
+          <t>Instructivo Técnico para Diagnóstico de PRRS mediante ELISA (D-GF-CGP-PT-017)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://journals.plos.org/plosone/article?id=10.1371/journal.pone.0181569</t>
+          <t>https://www.sag.gob.cl/sites/default/files/it_diagnostico_prrs_mediante_elisa_v02.pdf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -44326,7 +44301,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>B12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -44341,12 +44316,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Características hematológicas y patológicas de cerdos inoculados experimentalmente con el aislado chileno del virus síndrome respiratorio y reproductivo porcino</t>
+          <t>Resolución Exenta 2114/2023 (Bioseguridad)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.scielo.cl/scielo.php?script=sci_arttext&amp;pid=S0301-732X2006000200009</t>
+          <t>https://www.bcn.cl/leychile/navegar?idNorma=1191355</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -44363,7 +44338,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -44378,12 +44353,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Resolución 2113 Exenta (16-ABR-2024)</t>
+          <t>A Review of Swine Breeding Herd Biosecurity in the United States to Prevent Virus Entry Using Porcine Reproductive and Respiratory Syndrome Virus as a Model Pathogen (Dee et al., 2024)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1202659</t>
+          <t>https://www.mdpi.com/2076-2615/14/18/2694</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -44400,7 +44375,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -44415,12 +44390,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Decreto 389 Exento (14-NOV-2014)</t>
+          <t>Improvements in swine herd biosecurity reduce incidence risk of porcine reproductive and respiratory syndrome virus in breeding herds in the Midwestern United States (Dee et al., JAVMA, 2024)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1070774</t>
+          <t>https://avmajournals.avma.org/view/journals/javma/262/4/javma.23.08.0437.xml</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -44437,7 +44412,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>B10</t>
+          <t>B15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -44452,12 +44427,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DTO-235: Reglamento para la erradicación del Síndrome Reproductivo y Respiratorio Porcino (PRRS)</t>
+          <t>Systematic review of the elimination methods of porcine reproductive and respiratory syndrome virus at the sow farm and regional levels (Pepin et al., 2026)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=194922</t>
+          <t>https://avmajournals.avma.org/view/journals/javma/264/6/javma.25.10.0711.xml</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -44474,7 +44449,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -44489,12 +44464,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Instructivo Técnico para Diagnóstico de PRRS mediante ELISA (D-GF-CGP-PT-017)</t>
+          <t>Origen del PRRS en Chile, la enfermedad de mayor relevancia en industria porcina</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/it_diagnostico_prrs_mediante_elisa_v02.pdf</t>
+          <t>https://veterinaria.uchile.cl/noticias/136015/origen-del-prrs-en-chile-la-mayor-enfermedad-en-la-industria-porcina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -44511,7 +44486,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>B12</t>
+          <t>B17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -44526,12 +44501,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Resolución Exenta 2114/2023 (Bioseguridad)</t>
+          <t>Síndrome reproductivo y respiratorio del cerdo (PRRS). Revisión (2015)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1191355</t>
+          <t>https://www.scielo.org.mx/scielo.php?pid=S2007-11242015000100005&amp;script=sci_arttext</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -44548,7 +44523,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -44563,12 +44538,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A Review of Swine Breeding Herd Biosecurity in the United States to Prevent Virus Entry Using Porcine Reproductive and Respiratory Syndrome Virus as a Model Pathogen (Dee et al., 2024)</t>
+          <t>Review on the transmission PRRSV between pigs and farms and impact on vaccination (Pileri &amp; Mateu, 2016)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2076-2615/14/18/2694</t>
+          <t>https://link.springer.com/article/10.1186/s13567-016-0391-4</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -44585,7 +44560,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -44600,12 +44575,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Improvements in swine herd biosecurity reduce incidence risk of porcine reproductive and respiratory syndrome virus in breeding herds in the Midwestern United States (Dee et al., JAVMA, 2024)</t>
+          <t>Survival of PRRSV in the Environment (Lugo Mesa et al., 2024)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://avmajournals.avma.org/view/journals/javma/262/4/javma.23.08.0437.xml</t>
+          <t>https://www.mdpi.com/2306-7381/11/1/22</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -44622,7 +44597,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>B15</t>
+          <t>B20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -44637,12 +44612,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Systematic review of the elimination methods of porcine reproductive and respiratory syndrome virus at the sow farm and regional levels (Pepin et al., 2026)</t>
+          <t>Direct and indirect pathways for the spread of African swine fever and other porcine infectious diseases: An application of the mental models approach (Galli et al., 2022)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://avmajournals.avma.org/view/journals/javma/264/6/javma.25.10.0711.xml</t>
+          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/tbed.14605</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -44659,7 +44634,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>B16</t>
+          <t>B21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -44674,12 +44649,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Origen del PRRS en Chile, la enfermedad de mayor relevancia en industria porcina</t>
+          <t>Prevalencia del síndrome reproductivo y respiratorio porcino (PRRS) en el sector de Pucchun – Camaná, Arequipa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://veterinaria.uchile.cl/noticias/136015/origen-del-prrs-en-chile-la-mayor-enfermedad-en-la-industria-porcina</t>
+          <t>https://repositorio.ucsm.edu.pe/items/a77caf47-0db9-42b4-a761-febaa86281d7</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -44696,7 +44671,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>B17</t>
+          <t>B22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -44711,12 +44686,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Síndrome reproductivo y respiratorio del cerdo (PRRS). Revisión (2015)</t>
+          <t>Porcine reproductive and respiratory disease virus: Evolution and recombination yields distinct ORF5 RFLP 1-7-4 viruses with individual pathogenicity</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.scielo.org.mx/scielo.php?pid=S2007-11242015000100005&amp;script=sci_arttext</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0042682217303458?via%3Dihub</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -44733,7 +44708,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B18</t>
+          <t>B23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -44748,12 +44723,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Review on the transmission PRRSV between pigs and farms and impact on vaccination (Pileri &amp; Mateu, 2016)</t>
+          <t>Porcine reproductive and respiratory syndrome (PRRS) regional awareness</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://link.springer.com/article/10.1186/s13567-016-0391-4</t>
+          <t>https://openknowledge.fao.org/server/api/core/bitstreams/f352e58f-fc36-4c9e-8065-e47dd1af9240/content</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -44770,7 +44745,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>B19</t>
+          <t>B24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -44785,12 +44760,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Survival of PRRSV in the Environment (Lugo Mesa et al., 2024)</t>
+          <t>Síndrome reproductivo y respiratorio porcino (PRRS) | SAG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2306-7381/11/1/22</t>
+          <t>https://www.sag.gob.cl/ambitos-de-accion/sindrome-reproductivo-y-respiratorio-porcino-prrs</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -44807,7 +44782,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>B20</t>
+          <t>B25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -44822,12 +44797,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Direct and indirect pathways for the spread of African swine fever and other porcine infectious diseases: An application of the mental models approach (Galli et al., 2022)</t>
+          <t>Protocolo de bioseguridad para la prevención y la diseminación del virus del síndrome respiratorio y reproductivo porcino</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://onlinelibrary.wiley.com/doi/full/10.1111/tbed.14605</t>
+          <t>https://www.ciap.org.ar/Sitio/Archivos/PRRSV_BiosecurityManual_ES.pdf</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -44844,7 +44819,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>B21</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -44854,34 +44829,34 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eje B</t>
+          <t>Eje C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Prevalencia del síndrome reproductivo y respiratorio porcino (PRRS) en el sector de Pucchun – Camaná, Arequipa</t>
+          <t>Persistence of avian influenza viruses in water</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://repositorio.ucsm.edu.pe/items/a77caf47-0db9-42b4-a761-febaa86281d7</t>
+          <t>https://www.jstor.org/stable/1591428</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B22</t>
+          <t>C23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -44891,34 +44866,34 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eje B</t>
+          <t>Eje C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Porcine reproductive and respiratory disease virus: Evolution and recombination yields distinct ORF5 RFLP 1-7-4 viruses with individual pathogenicity</t>
+          <t>Codigo Sanitario para los Animales Terrestres, 15a edicion, Capitulo 2.7.12 (Influenza aviar)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0042682217303458?via%3Dihub</t>
+          <t>https://www.aphis.usda.gov/sites/default/files/hpai-depopulation-disposal.pdf</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B23</t>
+          <t>C25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -44928,34 +44903,34 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Eje B</t>
+          <t>Eje C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Porcine reproductive and respiratory syndrome (PRRS) regional awareness</t>
+          <t>Evolution and ecology of influenza A viruses</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://openknowledge.fao.org/server/api/core/bitstreams/f352e58f-fc36-4c9e-8065-e47dd1af9240/content</t>
+          <t>https://journals.asm.org/journal/mr</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B24</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -44965,34 +44940,34 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Eje B</t>
+          <t>Eje C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Síndrome reproductivo y respiratorio porcino (PRRS) | SAG</t>
+          <t>Approaches to Controlling, Preventing and Eliminating H5N1 Highly Pathogenic Avian Influenza in Endemic Countries (FAO Animal Production and Health Paper N 171)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/ambitos-de-accion/sindrome-reproductivo-y-respiratorio-porcino-prrs</t>
+          <t>https://www.fao.org/</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B25</t>
+          <t>C29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -45002,34 +44977,34 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Eje B</t>
+          <t>Eje C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Protocolo de bioseguridad para la prevención y la diseminación del virus del síndrome respiratorio y reproductivo porcino</t>
+          <t>Lineamientos tecnico-operativos: Vacunacion antiinfluenza 2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.ciap.org.ar/Sitio/Archivos/PRRSV_BiosecurityManual_ES.pdf</t>
+          <t>https://vacunas.minsal.cl/</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -45044,12 +45019,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>recombination yields distinct ORF5 RFLP 1-7-4 viruses with individual</t>
+          <t>Resolucion Exenta N 7.695/2024: Actualiza manuales de bioseguridad para el rubro avicola</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.woah.org/es/enfermedad/influenza-aviar/</t>
+          <t>https://sag.cl/sites/default/files/R.E.%20N%C2%B07695-2024%20Bioseguridad%20en%20aves_0.pdf</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -45066,7 +45041,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -45081,10 +45056,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>pathogenicity</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Diseases of Poultry, 14a edicion</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.who.int/es/news-room/fact-sheets/detail/influenza-(avian-and-other-zoonotic)</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>Corregir URL</t>
@@ -45099,7 +45078,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -45109,17 +45088,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Persistence of avian influenza viruses in water</t>
+          <t>Manual de toma, conservacion y envio de muestras al laboratorio para enfermedades comunes de los animales (Anexo 4)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.jstor.org/stable/1591428</t>
+          <t>https://vacunas.minsal.cl/</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -45136,7 +45115,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -45146,30 +45125,34 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Codigo Sanitario para los Animales Terrestres, 15a edicion, Capitulo 2.7.12 (Influenza aviar)</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>Programa de control y monitoreo para el Sindrome Respiratorio y Reproductivo Porcino (PRRS): protocolos de diagnostico y estabilizacion de granjas</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.porkcolombia.co/</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C25</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -45179,17 +45162,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Evolution and ecology of influenza A viruses</t>
+          <t>Guia sobre la reglamentacion relativa al transporte de sustancias infecciosas 2019-2020</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://journals.asm.org/journal/mr</t>
+          <t>https://apps.who.int/iris</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -45206,7 +45189,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -45216,17 +45199,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Approaches to Controlling, Preventing and Eliminating H5N1 Highly Pathogenic Avian Influenza in Endemic Countries (FAO Animal Production and Health Paper N 171)</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 1.1.5: Gestion de calidad en los laboratorios de pruebas veterinarias</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.fao.org/</t>
+          <t>https://www.woah.org/es/que-hacemos/normas/codigos-y-manuales/</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -45243,7 +45226,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C29</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -45253,17 +45236,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lineamientos tecnico-operativos: Vacunacion antiinfluenza 2025</t>
+          <t>IDEXX Reference Laboratories: Specimen Collection Guidelines</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://vacunas.minsal.cl/</t>
+          <t>https://www.idexx.com/</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -45280,7 +45263,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>D10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -45290,17 +45273,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Resolucion Exenta N 7.695/2024: Actualiza manuales de bioseguridad para el rubro avicola</t>
+          <t>Codes and Manuals: Terrestrial Manual, Capitulo 1.1.2 Collection, submission and storage of diagnostic specimens</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/</t>
+          <t>https://www.woah.org/en/what-we-do/standards/codes-and-manuals/</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -45317,7 +45300,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -45327,30 +45310,34 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Eje C</t>
+          <t>Eje D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Diseases of Poultry, 14a edicion</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>IDEXX PRRS X3 - Porcine Reproductive and Respiratory Syndrome Virus Antibody Test Kit (inserto 06-40959-08)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/idexx-ws-web-documents/org/lpd-web-insert/idexx%20prrs%20x3%20ab%20test%20%28ous%29-06-40959-08.pdf</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -45365,25 +45352,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Manual de toma, conservacion y envio de muestras al laboratorio para enfermedades comunes de los animales (Anexo 4)</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>IDEXX PRRS X3 Ab Test - pagina de producto</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://al.idexx.com/es-xl/livestock/livestock-tests/swine-tests/idexx-prrs-x3-ab-test/</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -45398,29 +45389,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Instructivo Tecnico para el Diagnostico de PRRS mediante ELISA (D-GF-CGP-PT-017, version 02)</t>
+          <t>Best practices for using the IDEXX PRRS Oral Fluids Ab Test</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/it_diagnostico_prrs_mediante_elisa_v02.pdf</t>
+          <t>https://www.idexx.com/files/idexx-prrs-tips.pdf</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -45435,29 +45426,29 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Plan de Contingencia Influenza Aviar (IA), Version 6.0</t>
+          <t>IDEXX PRRS Oral Fluids Ab Test (North America) - pagina de producto</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/</t>
+          <t>https://www.idexx.com/en/livestock/livestock-tests/swine-tests/idexx-prrs-oral-fluids-ab-test-na/</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -45472,12 +45463,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programa de control y monitoreo para el Sindrome Respiratorio y Reproductivo Porcino (PRRS): protocolos de diagnostico y estabilizacion de granjas</t>
+          <t>Manual Terrestre de la OMSA, Capitulo 3.9.6: Sindrome reproductivo y respiratorio porcino (PRRS)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.porkcolombia.co/</t>
+          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/3.09.06_PRRS.pdf</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -45494,7 +45485,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -45509,29 +45500,29 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Guia sobre la reglamentacion relativa al transporte de sustancias infecciosas 2019-2020</t>
+          <t>Field application of a commercial PRRSV oral fluid antibody ELISA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://apps.who.int/iris</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7074113/</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -45546,29 +45537,29 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 1.1.5: Gestion de calidad en los laboratorios de pruebas veterinarias</t>
+          <t>Kinetics of the PRRSV humoral immune response in swine serum and oral fluids collected from individual boars</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.woah.org/es/que-hacemos/normas/codigos-y-manuales/</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3666961/</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>D25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -45583,29 +45574,29 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>IDEXX Reference Laboratories: Specimen Collection Guidelines</t>
+          <t>Evaluation of three commercially available influenza A type specific blocking ELISAs for seroepidemiological studies of influenza A virus infection in pigs</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/</t>
+          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3294623/</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -45620,12 +45611,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Codes and Manuals: Terrestrial Manual, Capitulo 1.1.2 Collection, submission and storage of diagnostic specimens</t>
+          <t>RealPCR Influenza A RNA Mix - mezcla de partidores y sonda para PCR en tiempo real (inserto 06-56200-02)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.woah.org/en/what-we-do/standards/codes-and-manuals/</t>
+          <t>https://www.idexx.com/</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -45642,7 +45633,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>D12</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -45657,12 +45648,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>IDEXX PRRS X3 - Porcine Reproductive and Respiratory Syndrome Virus Antibody Test Kit (inserto 06-40959-08)</t>
+          <t>RealPCR PRRSV Type 1 and Type 2 Multiplex RNA Test (inserto 06-56645-02)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://s3.amazonaws.com/idexx-ws-web-documents/org/lpd-web-insert/idexx%20prrs%20x3%20ab%20test%20%28ous%29-06-40959-08.pdf</t>
+          <t>https://www.idexx.com/</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -45679,7 +45670,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -45694,29 +45685,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>IDEXX PRRS X3 Ab Test - pagina de producto</t>
+          <t>RealPCR Technical Guide</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://al.idexx.com/es-xl/livestock/livestock-tests/swine-tests/idexx-prrs-x3-ab-test/</t>
+          <t>https://www.idexx.com/</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -45731,12 +45722,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Best practices for using the IDEXX PRRS Oral Fluids Ab Test</t>
+          <t>Guidelines for oral fluid-based surveillance of viral pathogens in swine</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/files/idexx-prrs-tips.pdf</t>
+          <t>https://doi.org/10.1186/s40813-020-00168-w</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -45753,7 +45744,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -45768,12 +45759,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>IDEXX PRRS Oral Fluids Ab Test (North America) - pagina de producto</t>
+          <t>The use of oral fluid diagnostics in swine medicine</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/en/livestock/livestock-tests/swine-tests/idexx-prrs-oral-fluids-ab-test-na/</t>
+          <t>https://www.aasv.org/shap.html</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -45790,7 +45781,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -45805,12 +45796,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Manual Terrestre de la OMSA, Capitulo 3.9.6: Sindrome reproductivo y respiratorio porcino (PRRS)</t>
+          <t>Swine practitioner practices on oral fluid sampling in U.S. swine farms: a nationwide survey</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.woah.org/fileadmin/Home/eng/Health_standards/tahm/3.09.06_PRRS.pdf</t>
+          <t>https://doi.org/10.3390/pathogens14090940</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -45827,7 +45818,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -45837,34 +45828,34 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Eje E</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Field application of a commercial PRRSV oral fluid antibody ELISA</t>
+          <t>ORD. B38/N° 5914 – Indica orientaciones operativas a los equipos de las SEREMI de Salud asociadas a los casos de influenza aviar (H5N1) en animales</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC7074113/</t>
+          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>E12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -45874,34 +45865,34 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Eje E</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kinetics of the PRRSV humoral immune response in swine serum and oral fluids collected from individual boars</t>
+          <t>ORD. B51 – Envía protocolo ante detección de expuestos a influenza aviar en contexto de alerta por hallazgos de IA en aves en Chile (incluye Protocolo de investigación de expuestos)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3666961/</t>
+          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>D25</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -45911,34 +45902,34 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Eje E</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Evaluation of three commercially available influenza A type specific blocking ELISAs for seroepidemiological studies of influenza A virus infection in pigs</t>
+          <t>ORD. B38/N° 536 – Envía orientaciones de prevención ambiental y ocupacional en el contexto del brote de influenza aviar</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC3294623/</t>
+          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>E14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -45948,34 +45939,34 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Eje E</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Plan Anual de Vigilancia de Enfermedades Exoticas 2026 (Version 1)</t>
+          <t>ORD. B51 N° 1022 – Refuerza la alerta, vigilancia epidemiológica y flujo de atención de casos sospechosos en personas frente a animales positivos a influenza aviar</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/</t>
+          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Corregir URL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Prioridad: Corregir URL</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>D28</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -45985,17 +45976,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Eje E</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>RealPCR Influenza A RNA Mix - mezcla de partidores y sonda para PCR en tiempo real (inserto 06-56200-02)</t>
+          <t>ORD. B38/N° 169 – Envía flujograma de comunicaciones entre áreas técnicas de las instituciones involucradas en hallazgos de influenza aviar de alta patogenicidad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/</t>
+          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -46012,101 +46003,101 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>D29</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Climático-ambiental</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>RealPCR PRRSV Type 1 and Type 2 Multiplex RNA Test (inserto 06-56645-02)</t>
+          <t>Spatio-temporal dynamics and drivers of highly pathogenic avian influenza H5N1 in Chile</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/</t>
+          <t>https://doi.org/10.3389/fvets.2024.1387040</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Duplicado</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Prioridad: Duplicado</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>CLI-026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Climático-ambiental</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>RealPCR Technical Guide</t>
+          <t>Spatio-temporal dynamics and drivers of highly pathogenic avian influenza H5N1 in Chile.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.idexx.com/</t>
+          <t>https://doi.org/10.3389/fvets.2024.1387040</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Duplicado</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Prioridad: Duplicado</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D-PM228</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Diagnóstico</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Guidelines for oral fluid-based surveillance of viral pathogens in swine</t>
+          <t>Serological Evidence of Backyard Pig Exposure to Highly Pathogenic Avian Influenza H5N8 Virus during 2016-2017 Epizootic in France.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s40813-020-00168-w</t>
+          <t>https://doi.org/10.3390/pathogens10050621</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -46123,27 +46114,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D-PM375</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Diagnóstico</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The use of oral fluid diagnostics in swine medicine</t>
+          <t>Quantifying iris pigmentation irregularities following an avian influenza outbreak: implications for population-level disease surveillance in a colonial seabird.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.aasv.org/shap.html</t>
+          <t>https://doi.org/10.1093/conphys/coag069</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -46160,27 +46151,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>BIO-062</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eje D</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Swine practitioner practices on oral fluid sampling in U.S. swine farms: a nationwide survey</t>
+          <t>Patterns and risk factors of avian influenza A (H5) and A (H9) virus infection in pigeons and quail at live bird markets in Bangladesh, 2017–2021</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/pathogens14090940</t>
+          <t>https://doi.org/10.3389/fvets.2022.1016970</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -46197,414 +46188,414 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>BIO-119</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Decreto 389 EXENTO – Establece enfermedades de declaración obligatoria para la aplicación de medidas sanitarias</t>
+          <t>From RAGs to riches: utilizing large language models to write documents for clinical trials</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1070774</t>
+          <t>https://doi.org/10.1177/17407745251320806</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>BIO-121</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Plan de Contingencia Influenza Aviar – Versión 6.0</t>
+          <t>LLM-augmented multi-agent cooperative framework for medical case retrieval in cardiology</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/content/plan-de-contingencia-influenza-aviar</t>
+          <t>https://doi.org/10.1007/s44443-025-00311-z</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>BIO-123</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Resolución Exenta N° 2.113/2024 – Declara a Chile país libre del Síndrome Reproductivo y Respiratorio Porcino (PRRS)</t>
+          <t>BIOGEN: evidence-grounded multi-agent reasoning framework for transcriptomic interpretation in antimicrobial resistance</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=1202659&amp;idParte=&amp;idVersion=2024-04-16</t>
+          <t>https://doi.org/10.3389/fbinf.2026.1846404</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>BIO-128</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Decreto 235 – Reglamento para la erradicación del Síndrome Disgenésico y Respiratorio del Cerdo (PRRS)</t>
+          <t>Design and multidimensional expert evaluation of a national health information portal-integrated generative AI chatbot for health literacy and awareness</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/navegar?idNorma=194922</t>
+          <t>https://doi.org/10.1177/20552076261481326</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>BIO-129</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Instructivo Técnico para el diagnóstico de PRRS mediante ELISA (código D-GF-CGP-PT-017, versión 02)</t>
+          <t>Dynamic alignment of large language models for evidence-grounded heart failure decision support</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.sag.gob.cl/sites/default/files/it_diagnostico_prrs_mediante_elisa_v02.pdf</t>
+          <t>https://doi.org/10.1177/20552076261487568</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>E11</t>
+          <t>BIO-130</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ORD. B38/N° 5914 – Indica orientaciones operativas a los equipos de las SEREMI de Salud asociadas a los casos de influenza aviar (H5N1) en animales</t>
+          <t>Toward an integrated animal–human nutrition intelligence via agentic retrieval-augmented language models</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
+          <t>https://doi.org/10.3389/fnut.2026.1815038</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>E12</t>
+          <t>BIO-131</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ORD. B51 – Envía protocolo ante detección de expuestos a influenza aviar en contexto de alerta por hallazgos de IA en aves en Chile (incluye Protocolo de investigación de expuestos)</t>
+          <t>MEGA-RAG: a retrieval-augmented generation framework with multi-evidence guided answer refinement for mitigating hallucinations of LLMs in public health</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
+          <t>https://doi.org/10.3389/fpubh.2025.1635381</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>BIO-133</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ORD. B38/N° 536 – Envía orientaciones de prevención ambiental y ocupacional en el contexto del brote de influenza aviar</t>
+          <t>GraphRAG-Vet: A Knowledge Graph-Augmented Large Language Model for Precision Bovine Disease Diagnosis</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
+          <t>https://doi.org/10.3390/computers15040203</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>BIO-134</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ORD. B51 N° 1022 – Refuerza la alerta, vigilancia epidemiológica y flujo de atención de casos sospechosos en personas frente a animales positivos a influenza aviar</t>
+          <t>An Adaptive Multi-Agent LLM-Based Clinical Decision Support System Integrating Biomedical RAG and Web Intelligence</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
+          <t>https://doi.org/10.1109/access.2025.3613340</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>BIO-135</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Eje E</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ORD. B38/N° 169 – Envía flujograma de comunicaciones entre áreas técnicas de las instituciones involucradas en hallazgos de influenza aviar de alta patogenicidad</t>
+          <t>A self-correcting Agentic Graph RAG for clinical decision support in hepatology</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.minsal.cl/repositorio-influenza-aviar-de-alta-patogenicidad/</t>
+          <t>https://doi.org/10.3389/fmed.2025.1716327</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Corregir URL</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Prioridad: Corregir URL</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>BIO-138</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Corpus RAG</t>
+          <t>Bibliometría</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Eje F</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Decreto 389 EXENTO: ESTABLECE ENFERMEDADES DE DECLARACIÓN OBLIGATORIA PARA LA APLICACIÓN DE MEDIDAS SANITARIAS</t>
+          <t>VAIV bio-discovery service using transformer model and retrieval augmented generation</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/leychile/Navegar/imprimir?idNorma=1070774&amp;idVersion=2019-07-02</t>
+          <t>https://doi.org/10.1186/s12859-024-05903-6</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>MOD_VER-019</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -46614,34 +46605,34 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Climático-ambiental</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Spatio-temporal dynamics and drivers of highly pathogenic avian influenza H5N1 in Chile</t>
+          <t>Benchmarking large language models for personalized, biomarker-based health intervention recommendations.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fvets.2024.1387040</t>
+          <t>https://doi.org/10.1038/s41746-025-01996-2</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CLI-026</t>
+          <t>MOD_VER-020</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -46651,34 +46642,34 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Climático-ambiental</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Spatio-temporal dynamics and drivers of highly pathogenic avian influenza H5N1 in Chile.</t>
+          <t>Evaluating clinical AI summaries with large language models as judges.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fvets.2024.1387040</t>
+          <t>https://doi.org/10.1038/s41746-025-02005-2</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Duplicado</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Prioridad: Duplicado</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>D-PM228</t>
+          <t>MOD_VER-021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -46688,34 +46679,34 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Diagnóstico</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Serological Evidence of Backyard Pig Exposure to Highly Pathogenic Avian Influenza H5N8 Virus during 2016-2017 Epizootic in France.</t>
+          <t>Benchmarking large language model-based agent systems for clinical decision tasks.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/pathogens10050621</t>
+          <t>https://doi.org/10.1038/s41746-026-02443-6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>D-PM375</t>
+          <t>MOD_VER-022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -46725,34 +46716,34 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Diagnóstico</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Quantifying iris pigmentation irregularities following an avian influenza outbreak: implications for population-level disease surveillance in a colonial seabird.</t>
+          <t>Automating Evaluation of AI Text Generation in Healthcare with a Large Language Model (LLM)-as-a-Judge.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1093/conphys/coag069</t>
+          <t>https://doi.org/10.1101/2025.04.22.25326219</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BIO-062</t>
+          <t>MOD_VER-029</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -46762,34 +46753,34 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Patterns and risk factors of avian influenza A (H5) and A (H9) virus infection in pigeons and quail at live bird markets in Bangladesh, 2017–2021</t>
+          <t>Agentic AI and Large Language Models in Radiology: Opportunities and Hallucination Challenges.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fvets.2022.1016970</t>
+          <t>https://doi.org/10.3390/bioengineering12121303</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BIO-119</t>
+          <t>MOD_VER-030</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -46799,34 +46790,34 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>From RAGs to riches: utilizing large language models to write documents for clinical trials</t>
+          <t>RAG in clinical practice: a cautionary tale of AI 'Truthfulness'.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/17407745251320806</t>
+          <t>https://doi.org/10.1038/s44401-026-00115-x</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BIO-121</t>
+          <t>MOD_VER-031</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -46836,34 +46827,34 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LLM-augmented multi-agent cooperative framework for medical case retrieval in cardiology</t>
+          <t>PlainQAFact: Retrieval-augmented factual consistency evaluation metric for biomedical plain language summarization.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s44443-025-00311-z</t>
+          <t>https://doi.org/10.1016/j.jbi.2026.105019</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BIO-123</t>
+          <t>MOD_VER-033</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -46873,17 +46864,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BIOGEN: evidence-grounded multi-agent reasoning framework for transcriptomic interpretation in antimicrobial resistance</t>
+          <t>Hyper-RAG: combating LLM hallucinations using hypergraph-driven retrieval-augmented generation.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fbinf.2026.1846404</t>
+          <t>https://doi.org/10.1038/s41467-026-71411-1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -46893,14 +46884,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BIO-128</t>
+          <t>MOD_VER-035</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -46910,34 +46901,34 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Design and multidimensional expert evaluation of a national health information portal-integrated generative AI chatbot for health literacy and awareness</t>
+          <t>Enhancing Large Language Model Reliability: Minimizing Hallucinations with Dual Retrieval-Augmented Generation Based on the Latest Diabetes Guidelines.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076261481326</t>
+          <t>https://doi.org/10.3390/jpm14121131</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BIO-129</t>
+          <t>MOD_VER-037</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -46947,17 +46938,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Dynamic alignment of large language models for evidence-grounded heart failure decision support</t>
+          <t>ChatTogoVar: a TogoVar-based retrieval-augmented generation system for precise genomic variant interpretation.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076261487568</t>
+          <t>https://doi.org/10.1038/s41439-026-00344-4</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -46967,14 +46958,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BIO-130</t>
+          <t>MOD_VER-038</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -46984,17 +46975,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Toward an integrated animal–human nutrition intelligence via agentic retrieval-augmented language models</t>
+          <t>A Multiagent Summarization and Auto-Evaluation Framework for Medical Text: Development and Evaluation Study.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fnut.2026.1815038</t>
+          <t>https://doi.org/10.2196/75932</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -47004,14 +46995,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BIO-131</t>
+          <t>MOD_VER-039</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -47021,17 +47012,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>MEGA-RAG: a retrieval-augmented generation framework with multi-evidence guided answer refinement for mitigating hallucinations of LLMs in public health</t>
+          <t>A Review of Multi-Agent AI Systems for Biological and Clinical Data Analysis.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fpubh.2025.1635381</t>
+          <t>https://doi.org/10.3390/mps9020033</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -47041,14 +47032,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BIO-133</t>
+          <t>MOD_VER-042</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -47058,34 +47049,34 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>GraphRAG-Vet: A Knowledge Graph-Augmented Large Language Model for Precision Bovine Disease Diagnosis</t>
+          <t>"A Midsummer Night's Dream" quest for truth: From ChatGPT "hallucinations" to RAG reasoning and ACURAI precision - a scoping review on detection, minimizing, and (almost) complete error elimination and enhancing Large Language Models' reliability</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/computers15040203</t>
+          <t>https://doi.org/10.12680/balneo.2025.847</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BIO-134</t>
+          <t>MOD_VER-044</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -47095,34 +47086,34 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>An Adaptive Multi-Agent LLM-Based Clinical Decision Support System Integrating Biomedical RAG and Web Intelligence</t>
+          <t>Medication Counseling with Large Language Models: Balancing Flexibility and Rigidity</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2025.3613340</t>
+          <t>https://doi.org/10.1109/ica67499.2025.00047</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BIO-135</t>
+          <t>MOD_VER-045</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -47132,17 +47123,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>A self-correcting Agentic Graph RAG for clinical decision support in hepatology</t>
+          <t>MedPAO: A Protocol-Driven Agent for Structuring Medical Reports</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fmed.2025.1716327</t>
+          <t>https://doi.org/10.1007/978-3-032-06004-4_4</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -47152,14 +47143,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BIO-138</t>
+          <t>MOD_VER-049</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -47169,17 +47160,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VAIV bio-discovery service using transformer model and retrieval augmented generation</t>
+          <t>Agentic AI in Healthcare: Current Applications, Challenges, and Future Directions</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1186/s12859-024-05903-6</t>
+          <t>https://doi.org/10.1109/access.2026.3725858</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -47189,14 +47180,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MOD_VER-019</t>
+          <t>MOD_VER-053</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -47211,12 +47202,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Benchmarking large language models for personalized, biomarker-based health intervention recommendations.</t>
+          <t>Multi-Agent collaboration as a complementary architecture for AI-generated medical examination items.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41746-025-01996-2</t>
+          <t>https://doi.org/10.1038/s41746-026-03187-z</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -47233,7 +47224,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MOD_VER-020</t>
+          <t>MOD_VER-056</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -47248,12 +47239,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Evaluating clinical AI summaries with large language models as judges.</t>
+          <t>Development and evaluation of an agentic LLM based RAG framework for evidence-based patient education.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41746-025-02005-2</t>
+          <t>https://doi.org/10.1136/bmjhci-2025-101570</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -47270,7 +47261,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MOD_VER-021</t>
+          <t>MOD_VER-062</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -47285,12 +47276,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Benchmarking large language model-based agent systems for clinical decision tasks.</t>
+          <t>Challenges and Solutions in Applying Large Language Models to Guideline-Based Management Planning and Automated Medical Coding in Health Care: Algorithm Development and Validation.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41746-026-02443-6</t>
+          <t>https://doi.org/10.2196/66691</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -47307,7 +47298,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MOD_VER-022</t>
+          <t>MOD_VER-067</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47322,12 +47313,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Automating Evaluation of AI Text Generation in Healthcare with a Large Language Model (LLM)-as-a-Judge.</t>
+          <t>Evaluating U.S. Federal Zoonotic Records Against National One Health Goals: A Multi-LLM Assessment Across COVID-19, Monkeypox, and H5N1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1101/2025.04.22.25326219</t>
+          <t>https://doi.org/10.3390/zoonoticdis6040040</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -47344,7 +47335,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MOD_VER-029</t>
+          <t>MOD_VER-069</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47359,12 +47350,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Agentic AI and Large Language Models in Radiology: Opportunities and Hallucination Challenges.</t>
+          <t>Exploring LLM Multi-Agents for ICD Coding</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/bioengineering12121303</t>
+          <t>https://doi.org/10.48550/arxiv.2406.15363</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -47381,7 +47372,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MOD_VER-030</t>
+          <t>MOD_VER-071</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -47396,12 +47387,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>RAG in clinical practice: a cautionary tale of AI 'Truthfulness'.</t>
+          <t>Zodiac: A Cardiologist-Level LLM Framework for Multi-Agent Diagnostics</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s44401-026-00115-x</t>
+          <t>https://doi.org/10.48550/arxiv.2410.02026</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -47418,7 +47409,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MOD_VER-031</t>
+          <t>MOD_VER-076</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -47433,17 +47424,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PlainQAFact: Retrieval-augmented factual consistency evaluation metric for biomedical plain language summarization.</t>
+          <t>Agentic Generative Artificial Intelligence System for Classification of Pathology-Confirmed Primary Progressive Aphasia Variants</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jbi.2026.105019</t>
+          <t>https://doi.org/10.1101/2025.10.28.25338977</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -47455,7 +47446,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MOD_VER-033</t>
+          <t>MOD_VER-077</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -47470,12 +47461,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Hyper-RAG: combating LLM hallucinations using hypergraph-driven retrieval-augmented generation.</t>
+          <t>Evaluating the AI Potential as a Safety Net for Diagnosis: A Novel Benchmark of Large Language Models in Correcting Diagnostic Errors</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41467-026-71411-1</t>
+          <t>https://doi.org/10.64898/2026.02.22.26346832</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -47492,7 +47483,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MOD_VER-035</t>
+          <t>MOD_VER-078</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -47507,12 +47498,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Enhancing Large Language Model Reliability: Minimizing Hallucinations with Dual Retrieval-Augmented Generation Based on the Latest Diabetes Guidelines.</t>
+          <t>CogRad: A Cognitively-Inspired Multi-Agent Framework for Radiology Report Generation</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/jpm14121131</t>
+          <t>https://doi.org/10.48550/arxiv.2607.03853</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -47529,7 +47520,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MOD_VER-037</t>
+          <t>MOD_VER-080</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -47544,17 +47535,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ChatTogoVar: a TogoVar-based retrieval-augmented generation system for precise genomic variant interpretation.</t>
+          <t>Care Plan Generation for Underserved Patients Using Multi-Agent Language Models: Applying Nash Game Theory to Optimize Multiple Objectives</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41439-026-00344-4</t>
+          <t>https://doi.org/10.64898/2026.02.23.26346934</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -47566,7 +47557,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MOD_VER-038</t>
+          <t>MOD_VER-083</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -47581,17 +47572,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>A Multiagent Summarization and Auto-Evaluation Framework for Medical Text: Development and Evaluation Study.</t>
+          <t>A MULTI-AGENT GENERATIVE AI FRAMEWORK FOR HEALTHCARE DECISION SUPPORT</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2196/75932</t>
+          <t>https://doi.org/10.4238/nf6pgw41</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -47603,7 +47594,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MOD_VER-039</t>
+          <t>MOD_VER-092</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -47618,12 +47609,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>A Review of Multi-Agent AI Systems for Biological and Clinical Data Analysis.</t>
+          <t>Hallucination to truth: a review of fact-checking and factuality evaluation in large language models</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/mps9020033</t>
+          <t>https://doi.org/10.1007/s10462-025-11454-w</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -47640,7 +47631,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MOD_VER-042</t>
+          <t>MOD_VER-096</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -47655,17 +47646,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>"A Midsummer Night's Dream" quest for truth: From ChatGPT "hallucinations" to RAG reasoning and ACURAI precision - a scoping review on detection, minimizing, and (almost) complete error elimination and enhancing Large Language Models' reliability</t>
+          <t>Dialectic-Med: Mitigating Diagnostic Hallucinations via Counterfactual Adversarial Multi-Agent Debate</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://doi.org/10.12680/balneo.2025.847</t>
+          <t>https://doi.org/10.48550/arxiv.2604.11258</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -47677,7 +47668,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MOD_VER-044</t>
+          <t>MOD_VER-099</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -47692,17 +47683,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Medication Counseling with Large Language Models: Balancing Flexibility and Rigidity</t>
+          <t>Chain-based Adaptive Reconfiguration Over Lattices for Hallucination Reduction</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ica67499.2025.00047</t>
+          <t>https://doi.org/10.48550/arxiv.2605.27706</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -47714,7 +47705,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MOD_VER-045</t>
+          <t>MOD_VER-102</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -47729,12 +47720,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>MedPAO: A Protocol-Driven Agent for Structuring Medical Reports</t>
+          <t>GSAR: Typed Grounding for Hallucination Detection and Recovery in Multi-Agent LLMs</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/978-3-032-06004-4_4</t>
+          <t>https://doi.org/10.48550/arxiv.2604.23366</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -47751,7 +47742,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MOD_VER-049</t>
+          <t>MOD_VER-104</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -47766,17 +47757,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Agentic AI in Healthcare: Current Applications, Challenges, and Future Directions</t>
+          <t>Detecting Hallucinations In LLM Responses Using Token-level Log-probability Signals</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2026.3725858</t>
+          <t>https://doi.org/10.66693/mathai.1025</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -47788,7 +47779,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MOD_VER-053</t>
+          <t>MOD_VER-107</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -47803,12 +47794,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Multi-Agent collaboration as a complementary architecture for AI-generated medical examination items.</t>
+          <t>AI Veterinary Assistance: Enhancing Clinical Decision-Making in Animal Healthcare</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41746-026-03187-z</t>
+          <t>https://doi.org/10.1109/access.2025.3587787</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -47825,7 +47816,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MOD_VER-056</t>
+          <t>MOD_VER-117</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -47840,17 +47831,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Development and evaluation of an agentic LLM based RAG framework for evidence-based patient education.</t>
+          <t>DoctorAgent-RL: A Multi-Agent Collaborative Reinforcement Learning System for Multi-Turn Clinical Dialogue</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1136/bmjhci-2025-101570</t>
+          <t>https://doi.org/10.1109/icassp55912.2026.11460976</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -47862,7 +47853,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MOD_VER-062</t>
+          <t>MOD_VER-134</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -47877,17 +47868,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Challenges and Solutions in Applying Large Language Models to Guideline-Based Management Planning and Automated Medical Coding in Health Care: Algorithm Development and Validation.</t>
+          <t>BioMedSearch: A Multi-Source Biomedical Retrieval Framework Based on LLMs</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2196/66691</t>
+          <t>https://doi.org/10.1109/bibm66473.2025.11356779</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -47899,456 +47890,456 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MOD_VER-067</t>
+          <t>BIO-117</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Evaluating U.S. Federal Zoonotic Records Against National One Health Goals: A Multi-LLM Assessment Across COVID-19, Monkeypox, and H5N1</t>
+          <t>Answering real-world clinical questions using large language model, retrieval-augmented generation, and agentic systems</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/zoonoticdis6040040</t>
+          <t>https://doi.org/10.1177/20552076251348850</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MOD_VER-069</t>
+          <t>BIO-120</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Exploring LLM Multi-Agents for ICD Coding</t>
+          <t>Evaluating adherence to Canadian radiology guidelines for incidental hepatobiliary findings using RAG-enabled LLMs</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2406.15363</t>
+          <t>https://doi.org/10.1177/08465371251323124</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MOD_VER-071</t>
+          <t>BIO-122</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Zodiac: A Cardiologist-Level LLM Framework for Multi-Agent Diagnostics</t>
+          <t>Performance of latest AI models, RAG, and MCP on lung cancer-related questions</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2410.02026</t>
+          <t>https://doi.org/10.1177/20552076261427503</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MOD_VER-076</t>
+          <t>BIO-124</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Agentic Generative Artificial Intelligence System for Classification of Pathology-Confirmed Primary Progressive Aphasia Variants</t>
+          <t>A Chatbot for the Management of Bipolar Disorder: Using Retrieval-Augmented Generation With an Open-Weight Large Language Model to Answer Clinical Questions Based on the CANMAT and ISBD 2018 Guidelines for Bipolar Disorder: Un dialogueur pour la prise en charge du trouble bipolaire : utiliser la génération augmentée par récupération avec un grand modèle de langage (GML) à poids ouverts pour répondre aux questions cliniques fondées sur les lignes directrices de 2018 de CANMAT et de l'ISBD relatives au trouble bipolaire</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1101/2025.10.28.25338977</t>
+          <t>https://doi.org/10.1177/07067437261457232</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MOD_VER-077</t>
+          <t>BIO-125</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Evaluating the AI Potential as a Safety Net for Diagnosis: A Novel Benchmark of Large Language Models in Correcting Diagnostic Errors</t>
+          <t>Development of a cancer information chatbot model: Retrieval-augmented generation with data from the national center for cancer knowledge and information</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://doi.org/10.64898/2026.02.22.26346832</t>
+          <t>https://doi.org/10.1177/20552076261450314</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MOD_VER-078</t>
+          <t>BIO-126</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>CogRad: A Cognitively-Inspired Multi-Agent Framework for Radiology Report Generation</t>
+          <t>Improved accuracy and efficiency of guideline-based orthopedic disability assessment with a retrieval-augmented AI assistant (NotebookLM) in anonymized cases</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2607.03853</t>
+          <t>https://doi.org/10.1177/20552076261473719</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MOD_VER-080</t>
+          <t>BIO-127</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Care Plan Generation for Underserved Patients Using Multi-Agent Language Models: Applying Nash Game Theory to Optimize Multiple Objectives</t>
+          <t>Performance and usability of retrieval-augmented large language models for stroke patient and caregiver support</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://doi.org/10.64898/2026.02.23.26346934</t>
+          <t>https://doi.org/10.1177/20552076261464997</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MOD_VER-083</t>
+          <t>BIO-132</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>A MULTI-AGENT GENERATIVE AI FRAMEWORK FOR HEALTHCARE DECISION SUPPORT</t>
+          <t>Use of Retrieval-Augmented Large Language Model for COVID-19 Fact-Checking: Development and Usability Study</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://doi.org/10.4238/nf6pgw41</t>
+          <t>https://doi.org/10.2196/66098</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MOD_VER-092</t>
+          <t>BIO-136</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Hallucination to truth: a review of fact-checking and factuality evaluation in large language models</t>
+          <t>A novel context-aware retrieval framework for biomedical knowledge integration with large language models</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s10462-025-11454-w</t>
+          <t>https://doi.org/10.1016/j.inffus.2025.103902</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MOD_VER-096</t>
+          <t>BIO-137</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Dialectic-Med: Mitigating Diagnostic Hallucinations via Counterfactual Adversarial Multi-Agent Debate</t>
+          <t>Using large language models to assist antimicrobial resistance policy development: Integrating the environment into health protection planning</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2604.11258</t>
+          <t>https://doi.org/10.1021/acs.est.4c07842</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MOD_VER-099</t>
+          <t>BIO-139</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Bioseguridad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Chain-based Adaptive Reconfiguration Over Lattices for Hallucination Reduction</t>
+          <t>Retrieval augmented generation system for mental health information</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2605.27706</t>
+          <t>https://doi.org/10.3233/shti250929</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Excluido a mano: paper de LLM/salud mental en bioseguridad (para revisar por Investigación)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MOD_VER-102</t>
+          <t>D-PM147</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Moderador-verificador</t>
+          <t>Diagnóstico</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>GSAR: Typed Grounding for Hallucination Detection and Recovery in Multi-Agent LLMs</t>
+          <t>Serological Evidence of Highly Pathogenic Avian Influenza (H5N1) in Invasive Wild Pigs in Western Canada.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://doi.org/10.48550/arxiv.2604.23366</t>
+          <t>https://doi.org/10.1155/tbed/2720469</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja (porcino)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
+          <t>Prioridad: Baja (porcino)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MOD_VER-104</t>
+          <t>MOD_VER-027</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -48358,12 +48349,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Detecting Hallucinations In LLM Responses Using Token-level Log-probability Signals</t>
+          <t>Enhanced LLM-supported instructions for medication use through retrieval-augmented generation.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://doi.org/10.66693/mathai.1025</t>
+          <t>https://doi.org/10.1016/j.compbiomed.2025.111135</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -48380,12 +48371,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MOD_VER-107</t>
+          <t>MOD_VER-028</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -48395,17 +48386,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AI Veterinary Assistance: Enhancing Clinical Decision-Making in Animal Healthcare</t>
+          <t>Enhancing medical AI with retrieval-augmented generation: A mini narrative review.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2025.3587787</t>
+          <t>https://doi.org/10.1177/20552076251337177</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -48417,12 +48408,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MOD_VER-117</t>
+          <t>MOD_VER-032</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -48432,12 +48423,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>DoctorAgent-RL: A Multi-Agent Collaborative Reinforcement Learning System for Multi-Turn Clinical Dialogue</t>
+          <t>Retrieval-augmented generation for medication safety: A case study using drug package inserts.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/icassp55912.2026.11460976</t>
+          <t>https://doi.org/10.1016/j.ijmedinf.2026.106599</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -48454,12 +48445,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MOD_VER-134</t>
+          <t>MOD_VER-034</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Bibliometría</t>
+          <t>Cribado</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -48469,12 +48460,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>BioMedSearch: A Multi-Source Biomedical Retrieval Framework Based on LLMs</t>
+          <t>Performance evaluation of large language models in pediatric nephrology clinical decision support: a comprehensive assessment.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/bibm66473.2025.11356779</t>
+          <t>https://doi.org/10.1007/s00467-025-06819-w</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -48491,7 +48482,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BIO-117</t>
+          <t>MOD_VER-040</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -48501,17 +48492,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Answering real-world clinical questions using large language model, retrieval-augmented generation, and agentic systems</t>
+          <t>MedARC: Adaptive multi-agent refinement and collaboration for enhanced medical reasoning in large language models.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076251348850</t>
+          <t>https://doi.org/10.1016/j.ijmedinf.2025.106136</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -48521,14 +48512,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BIO-120</t>
+          <t>MOD_VER-041</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -48538,17 +48529,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Evaluating adherence to Canadian radiology guidelines for incidental hepatobiliary findings using RAG-enabled LLMs</t>
+          <t>Design and Multi-level Evaluation of MAP-X: a Medically Aligned, Patient-Centered AI Explanation System</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/08465371251323124</t>
+          <t>https://doi.org/10.1145/3772318.3790971</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -48558,14 +48549,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BIO-122</t>
+          <t>MOD_VER-043</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -48575,17 +48566,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Performance of latest AI models, RAG, and MCP on lung cancer-related questions</t>
+          <t>LADDER: Latent Attention and Decomposition for Deep Enhanced Retrieval in Medical Question-Answering Systems</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076261427503</t>
+          <t>https://doi.org/10.1007/978-3-031-97141-9_16</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -48595,14 +48586,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BIO-124</t>
+          <t>MOD_VER-046</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -48612,17 +48603,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>A Chatbot for the Management of Bipolar Disorder: Using Retrieval-Augmented Generation With an Open-Weight Large Language Model to Answer Clinical Questions Based on the CANMAT and ISBD 2018 Guidelines for Bipolar Disorder: Un dialogueur pour la prise en charge du trouble bipolaire : utiliser la génération augmentée par récupération avec un grand modèle de langage (GML) à poids ouverts pour répondre aux questions cliniques fondées sur les lignes directrices de 2018 de CANMAT et de l'ISBD relatives au trouble bipolaire</t>
+          <t>TreatRAG: A Framework for Personalized Treatment Recommendation</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/07067437261457232</t>
+          <t>https://doi.org/10.1145/3705328.3748022</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -48632,14 +48623,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BIO-125</t>
+          <t>MOD_VER-047</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -48649,17 +48640,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Development of a cancer information chatbot model: Retrieval-augmented generation with data from the national center for cancer knowledge and information</t>
+          <t>Towards Automatic Evaluation for LLMs' Clinical Capabilities: Metric, Data, and Algorithm</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076261450314</t>
+          <t>https://doi.org/10.1145/3637528.3671575</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -48669,14 +48660,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BIO-126</t>
+          <t>MOD_VER-051</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -48686,17 +48677,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Improved accuracy and efficiency of guideline-based orthopedic disability assessment with a retrieval-augmented AI assistant (NotebookLM) in anonymized cases</t>
+          <t>From prediction to action: a comprehensive survey on agentic AI in healthcare, foundation, application and challenges</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076261473719</t>
+          <t>https://doi.org/10.1108/IDD-09-2025-0235</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -48706,14 +48697,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BIO-127</t>
+          <t>MOD_VER-052</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -48723,17 +48714,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Performance and usability of retrieval-augmented large language models for stroke patient and caregiver support</t>
+          <t>MedXpert-CAD: A Multimodal Multi-agentic System for Clinical Imaging Analysis via Model Context Protocol LLM-Driven Agentic Workflows</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076261464997</t>
+          <t>https://doi.org/10.1007/978-3-032-06004-4_6</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -48743,14 +48734,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BIO-132</t>
+          <t>MOD_VER-054</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -48760,34 +48751,34 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Use of Retrieval-Augmented Large Language Model for COVID-19 Fact-Checking: Development and Usability Study</t>
+          <t>An autonomous multimodal AI agent for evidence-grounded ophthalmic diagnosis.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2196/66098</t>
+          <t>https://doi.org/10.1016/j.xcrm.2026.102969</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BIO-136</t>
+          <t>MOD_VER-057</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -48797,17 +48788,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>A novel context-aware retrieval framework for biomedical knowledge integration with large language models</t>
+          <t>Knowledge-Based Interpretation of Multi-Modal Clinical Findings: Evaluating a Local Agentic Bridge Between Worlds.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.inffus.2025.103902</t>
+          <t>https://doi.org/10.3233/SHTI260192</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -48817,14 +48808,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BIO-137</t>
+          <t>MOD_VER-060</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -48834,17 +48825,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Using large language models to assist antimicrobial resistance policy development: Integrating the environment into health protection planning</t>
+          <t>PathFound: An agentic multimodal model activating evidence-seeking pathological diagnosis.</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1021/acs.est.4c07842</t>
+          <t>https://doi.org/10.1016/j.media.2026.104200</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -48854,14 +48845,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/RAG en bioseguridad, no es base veterinaria (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BIO-139</t>
+          <t>MOD_VER-068</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -48871,17 +48862,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bioseguridad</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Retrieval augmented generation system for mental health information</t>
+          <t>AI-Powered Retrieval-Augmented Generation Framework with Large Language Models for Enhanced Public Health Response</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3233/shti250929</t>
+          <t>https://doi.org/10.1109/InCACCT65424.2025.11011436</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -48891,14 +48882,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Excluido a mano: paper de LLM/salud mental en bioseguridad (para revisar por Investigación)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>D-PM147</t>
+          <t>MOD_VER-081</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -48908,34 +48899,34 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Diagnóstico</t>
+          <t>Moderador-verificador</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Serological Evidence of Highly Pathogenic Avian Influenza (H5N1) in Invasive Wild Pigs in Western Canada.</t>
+          <t>EXAIM: Explainable AI Middleware for Real-Time Multi-Agent Clinical Decision Support</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1155/tbed/2720469</t>
+          <t>https://doi.org/10.1109/ICHI69079.2026.00109</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Baja (porcino)</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Prioridad: Baja (porcino)</t>
+          <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MOD_VER-027</t>
+          <t>MOD_VER-082</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -48950,12 +48941,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Enhanced LLM-supported instructions for medication use through retrieval-augmented generation.</t>
+          <t>Structure Matters: Evaluating Multi-Agents Orchestration in Generative Therapeutic Chatbots</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.compbiomed.2025.111135</t>
+          <t>https://doi.org/10.1145/3816046.3816273</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -48972,7 +48963,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MOD_VER-028</t>
+          <t>MOD_VER-085</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -48987,12 +48978,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Enhancing medical AI with retrieval-augmented generation: A mini narrative review.</t>
+          <t>Curriculum-Trained Vertical Agents for Italian Medical Question Answering</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1177/20552076251337177</t>
+          <t>https://doi.org/10.1145/3794786.3830763</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -49009,7 +49000,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MOD_VER-032</t>
+          <t>MOD_VER-086</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -49024,12 +49015,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Retrieval-augmented generation for medication safety: A case study using drug package inserts.</t>
+          <t>Evaluating the Safety of Local LLM-Generated Exercise Prescriptions Against Clinical Guidelines</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijmedinf.2026.106599</t>
+          <t>https://doi.org/10.1109/SEGAH69272.2026.11653312</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -49046,7 +49037,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>MOD_VER-034</t>
+          <t>MOD_VER-087</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -49061,12 +49052,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Performance evaluation of large language models in pediatric nephrology clinical decision support: a comprehensive assessment.</t>
+          <t>Retrieval-LLM-Symbolic: A Dynamic Neuro-Symbolic Framework for Explainable and Time-Aware Medical QA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s00467-025-06819-w</t>
+          <t>https://doi.org/10.1145/3804601.3804680</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -49083,7 +49074,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MOD_VER-040</t>
+          <t>MOD_VER-088</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -49098,12 +49089,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>MedARC: Adaptive multi-agent refinement and collaboration for enhanced medical reasoning in large language models.</t>
+          <t>A Safety-Orchestrated Architecture for Large Language Models-Based Remote Healthcare Guidance</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ijmedinf.2025.106136</t>
+          <t>https://doi.org/10.1109/ICSA-C68850.2026.00025</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -49120,7 +49111,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MOD_VER-041</t>
+          <t>MOD_VER-091</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -49135,12 +49126,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Design and Multi-level Evaluation of MAP-X: a Medically Aligned, Patient-Centered AI Explanation System</t>
+          <t>A Generative AI Assistant for Infection Control: Integrating Large Language Models with Chatbots for Health Education</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3772318.3790971</t>
+          <t>https://doi.org/10.1109/COMPSAC69091.2026.00387</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -49157,7 +49148,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MOD_VER-043</t>
+          <t>MOD_VER-101</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -49172,12 +49163,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LADDER: Latent Attention and Decomposition for Deep Enhanced Retrieval in Medical Question-Answering Systems</t>
+          <t>Self-Auditing LLMs for Bias and Hallucination Reduction Through Multi-Agent Frameworks</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/978-3-031-97141-9_16</t>
+          <t>https://doi.org/10.1109/ICOECA68095.2026.11485555</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -49194,7 +49185,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MOD_VER-046</t>
+          <t>MOD_VER-103</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -49209,12 +49200,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>TreatRAG: A Framework for Personalized Treatment Recommendation</t>
+          <t>HalluXAI: A Claim-Level Multi-Agent Framework for Explainable Hallucination Detection in Large Language Models</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3705328.3748022</t>
+          <t>https://doi.org/10.1109/CIACON70148.2026.11689445</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -49231,7 +49222,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MOD_VER-047</t>
+          <t>MOD_VER-110</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -49246,12 +49237,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Towards Automatic Evaluation for LLMs' Clinical Capabilities: Metric, Data, and Algorithm</t>
+          <t>Telemedicine for Aquaculture Animal Health Using Artificial Intelligence (AI) in Thailand</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3637528.3671575</t>
+          <t>https://doi.org/10.1109/SNPD65828.2025.11252564</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -49268,7 +49259,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MOD_VER-051</t>
+          <t>MOD_VER-113</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -49283,12 +49274,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>From prediction to action: a comprehensive survey on agentic AI in healthcare, foundation, application and challenges</t>
+          <t>Collaboration among Multiple Large Language Models for Medical Question Answering</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1108/IDD-09-2025-0235</t>
+          <t>https://doi.org/10.1109/ICHI64645.2025.00052</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -49305,7 +49296,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MOD_VER-052</t>
+          <t>MOD_VER-114</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -49320,12 +49311,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>MedXpert-CAD: A Multimodal Multi-agentic System for Clinical Imaging Analysis via Model Context Protocol LLM-Driven Agentic Workflows</t>
+          <t>CARE-Agent: Multi-Agent Collaboration with Conflict-Aware Routing Mechanism for Diagnosis Prediction</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/978-3-032-06004-4_6</t>
+          <t>https://doi.org/10.1109/ICASSP55912.2026.11464147</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -49342,7 +49333,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MOD_VER-054</t>
+          <t>MOD_VER-115</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -49357,12 +49348,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>An autonomous multimodal AI agent for evidence-grounded ophthalmic diagnosis.</t>
+          <t>Towards the Reliability of Agentic Artificial Intelligence Models in Healthcare</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.xcrm.2026.102969</t>
+          <t>https://doi.org/10.1109/RAMS50514.2026.11424519</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -49379,7 +49370,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MOD_VER-057</t>
+          <t>MOD_VER-116</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -49394,12 +49385,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Knowledge-Based Interpretation of Multi-Modal Clinical Findings: Evaluating a Local Agentic Bridge Between Worlds.</t>
+          <t>A Dynamic Agent Framework for Large Language Model Reasoning for Medical and Visual Question Answering</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3233/SHTI260192</t>
+          <t>https://doi.org/10.1109/ICCVW69036.2025.00124</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -49416,7 +49407,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MOD_VER-060</t>
+          <t>MOD_VER-118</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -49431,12 +49422,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>PathFound: An agentic multimodal model activating evidence-seeking pathological diagnosis.</t>
+          <t>A Collaborative Agentic AI Framework for Complex Disease Diagnosis</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.media.2026.104200</t>
+          <t>https://doi.org/10.1109/ICA67499.2025.00058</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -49453,7 +49444,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MOD_VER-068</t>
+          <t>MOD_VER-119</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -49468,12 +49459,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AI-Powered Retrieval-Augmented Generation Framework with Large Language Models for Enhanced Public Health Response</t>
+          <t>Clinical Reasoning-Augmented Prediction: Agentic Verification Improves Reliability of VTE Detection from Radiology Reports</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/InCACCT65424.2025.11011436</t>
+          <t>https://doi.org/10.1109/ICDH72779.2026.00010</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -49490,7 +49481,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MOD_VER-081</t>
+          <t>MOD_VER-121</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -49505,12 +49496,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EXAIM: Explainable AI Middleware for Real-Time Multi-Agent Clinical Decision Support</t>
+          <t>Enhancing Medical Visual Question Answering with Explainable Knowledge Graphs and Agentic RAG</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICHI69079.2026.00109</t>
+          <t>https://doi.org/10.1109/NILES68063.2025.11232248</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -49527,7 +49518,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MOD_VER-082</t>
+          <t>MOD_VER-122</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -49542,12 +49533,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Structure Matters: Evaluating Multi-Agents Orchestration in Generative Therapeutic Chatbots</t>
+          <t>NCRAgent: A Neuro-Inspired Multiagent Framework for Transparent and Explainable Medical VQA</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3816046.3816273</t>
+          <t>https://doi.org/10.1109/TAI.2026.3668173</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -49564,7 +49555,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MOD_VER-085</t>
+          <t>MOD_VER-123</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -49579,12 +49570,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Curriculum-Trained Vertical Agents for Italian Medical Question Answering</t>
+          <t>Automated Medical Information Retrieval via Agentic Filter-and-Refine Pipeline</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3794786.3830763</t>
+          <t>https://doi.org/10.1109/SIU71813.2026.11636450</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -49601,7 +49592,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MOD_VER-086</t>
+          <t>MOD_VER-124</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -49616,12 +49607,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Evaluating the Safety of Local LLM-Generated Exercise Prescriptions Against Clinical Guidelines</t>
+          <t>Comparative Evaluation of Advanced RAG Architectures for Medical Question Answering</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/SEGAH69272.2026.11653312</t>
+          <t>https://doi.org/10.1109/ETCC69750.2026.11681946</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -49638,7 +49629,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MOD_VER-087</t>
+          <t>MOD_VER-127</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -49653,12 +49644,12 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Retrieval-LLM-Symbolic: A Dynamic Neuro-Symbolic Framework for Explainable and Time-Aware Medical QA</t>
+          <t>SelfRewardRAG: Enhancing Medical Reasoning with Retrieval-Augmented Generation and Self-Evaluation in Large Language Models</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1145/3804601.3804680</t>
+          <t>https://doi.org/10.1109/ISCV60512.2024.10620139</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -49675,7 +49666,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MOD_VER-088</t>
+          <t>MOD_VER-130</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -49690,12 +49681,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>A Safety-Orchestrated Architecture for Large Language Models-Based Remote Healthcare Guidance</t>
+          <t>SpecMedRAG: A Multi-Granularity Graph RAG for Specialty Medicine</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICSA-C68850.2026.00025</t>
+          <t>https://doi.org/10.1109/CW68232.2025.00061</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -49712,7 +49703,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MOD_VER-091</t>
+          <t>MOD_VER-131</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -49727,12 +49718,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>A Generative AI Assistant for Infection Control: Integrating Large Language Models with Chatbots for Health Education</t>
+          <t>Exploring RAGs Applications in Healthcare</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/COMPSAC69091.2026.00387</t>
+          <t>https://doi.org/10.1109/FLLM67465.2025.11391150</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -49749,7 +49740,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MOD_VER-101</t>
+          <t>MOD_VER-132</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -49764,12 +49755,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Self-Auditing LLMs for Bias and Hallucination Reduction Through Multi-Agent Frameworks</t>
+          <t>SearchRAG: Can Search Engines Be Helpful for LLM-Based Medical Question Answering?</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICOECA68095.2026.11485555</t>
+          <t>https://doi.org/10.1109/BIBM66473.2025.11356025</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -49786,7 +49777,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MOD_VER-103</t>
+          <t>MOD_VER-137</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -49801,12 +49792,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>HalluXAI: A Claim-Level Multi-Agent Framework for Explainable Hallucination Detection in Large Language Models</t>
+          <t>From Confidence to Care: Rule-Based Escalation for Trustworthy Clinical AI</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/CIACON70148.2026.11689445</t>
+          <t>https://doi.org/10.1109/CASCON66301.2025.00097</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -49823,7 +49814,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MOD_VER-110</t>
+          <t>MOD_VER-138</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -49838,12 +49829,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Telemedicine for Aquaculture Animal Health Using Artificial Intelligence (AI) in Thailand</t>
+          <t>Sanity-LLM: Enhancing Mental Health Chatbots with Retrieval-Augmented Generation (RAG)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/SNPD65828.2025.11252564</t>
+          <t>https://doi.org/10.1109/ICIMCIS68501.2025.11327020</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -49860,7 +49851,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MOD_VER-113</t>
+          <t>MOD_VER-139</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -49875,12 +49866,12 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Collaboration among Multiple Large Language Models for Medical Question Answering</t>
+          <t>Comparative Analysis of Multimodal RAG Deployment Strategies for Medical Image Understanding: API-Based, Local Fine-Tuning, and Hybrid Approaches</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICHI64645.2025.00052</t>
+          <t>https://doi.org/10.1109/AIxMHC65380.2025.00028</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -49897,7 +49888,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MOD_VER-114</t>
+          <t>MOD_VER-140</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -49912,12 +49903,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>CARE-Agent: Multi-Agent Collaboration with Conflict-Aware Routing Mechanism for Diagnosis Prediction</t>
+          <t>Structured Multimodal RAG: Document-Aware Retrieval and Alignment for Hallucination Mitigation</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICASSP55912.2026.11464147</t>
+          <t>https://doi.org/10.1109/AIAHPC66801.2025.11290404</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -49934,7 +49925,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>MOD_VER-115</t>
+          <t>MOD_VER-141</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -49949,12 +49940,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Towards the Reliability of Agentic Artificial Intelligence Models in Healthcare</t>
+          <t>AI Medical Health Assistant: Rag Approach</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/RAMS50514.2026.11424519</t>
+          <t>https://doi.org/10.1109/I2ITCON65200.2025.11210469</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -49971,7 +49962,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>MOD_VER-116</t>
+          <t>MOD_VER-143</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -49986,12 +49977,12 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>A Dynamic Agent Framework for Large Language Model Reasoning for Medical and Visual Question Answering</t>
+          <t>AI-Driven Differential Diagnosis: Leveraging RAG and LLMs in Intelligent Healthcare Systems</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICCVW69036.2025.00124</t>
+          <t>https://doi.org/10.1109/IE64880.2025.11130125</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -50008,7 +49999,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>MOD_VER-118</t>
+          <t>MOD_VER-144</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -50023,12 +50014,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>A Collaborative Agentic AI Framework for Complex Disease Diagnosis</t>
+          <t>A Tree-based RAG-Agent Recommendation System: A Case Study in Medical Test Data</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICA67499.2025.00058</t>
+          <t>https://doi.org/10.1109/ICCAI66501.2025.00106</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -50045,7 +50036,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>MOD_VER-119</t>
+          <t>MOD_VER-148</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -50060,12 +50051,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Clinical Reasoning-Augmented Prediction: Agentic Verification Improves Reliability of VTE Detection from Radiology Reports</t>
+          <t>Impact of Knowledge Source Type on RAG-Based LLMs in Specialized Medical Domains: A Case Study on Systemic Lupus Erythematosus</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICDH72779.2026.00010</t>
+          <t>https://doi.org/10.1109/IAICT71158.2026.11620937</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -50082,7 +50073,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MOD_VER-121</t>
+          <t>MOD_VER-149</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -50097,12 +50088,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Enhancing Medical Visual Question Answering with Explainable Knowledge Graphs and Agentic RAG</t>
+          <t>RAG-Based Knowledge Retrieval Architecture for Medical Web Platforms</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/NILES68063.2025.11232248</t>
+          <t>https://doi.org/10.1109/ISADES69945.2026.11608242</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -50119,7 +50110,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MOD_VER-122</t>
+          <t>MOD_VER-151</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -50134,12 +50125,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NCRAgent: A Neuro-Inspired Multiagent Framework for Transparent and Explainable Medical VQA</t>
+          <t>ClinixAI – A Rag-Powered Medical Assistant with Verified Clinical Insights</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/TAI.2026.3668173</t>
+          <t>https://doi.org/10.1109/ICADCS70036.2026.11582998</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -50156,7 +50147,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MOD_VER-123</t>
+          <t>MOD_VER-152</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -50171,12 +50162,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Automated Medical Information Retrieval via Agentic Filter-and-Refine Pipeline</t>
+          <t>Navigator: A Knowledge Graph and Agent-based Framework for Guiding Large Language Models toward Accurate and Reliable Medical Reasoning</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/SIU71813.2026.11636450</t>
+          <t>https://doi.org/10.1109/CSCWD68734.2026.11581682</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -50193,7 +50184,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MOD_VER-124</t>
+          <t>MOD_VER-154</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -50208,12 +50199,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Comparative Evaluation of Advanced RAG Architectures for Medical Question Answering</t>
+          <t>Design and Implementation of an Authoritative Medical QA System Based on Retrieval-Augmented Generation (RAG)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ETCC69750.2026.11681946</t>
+          <t>https://doi.org/10.1109/AIITA69518.2026.11567160</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -50230,7 +50221,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MOD_VER-127</t>
+          <t>MOD_VER-156</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -50245,12 +50236,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>SelfRewardRAG: Enhancing Medical Reasoning with Retrieval-Augmented Generation and Self-Evaluation in Large Language Models</t>
+          <t>Adapting Large Language Models for Healthcare with an Enhanced Retrieval-Augmented Generation Framework</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ISCV60512.2024.10620139</t>
+          <t>https://doi.org/10.1109/ICAACE65325.2025.11019949</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -50267,7 +50258,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MOD_VER-130</t>
+          <t>MOD_VER-158</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -50282,12 +50273,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SpecMedRAG: A Multi-Granularity Graph RAG for Specialty Medicine</t>
+          <t>MediTriR: A Triple-Driven Approach to Retrieval-Augmented Generation for Medical Question Answering Tasks</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/CW68232.2025.00061</t>
+          <t>https://doi.org/10.1109/ICSC64641.2025.00032</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -50304,7 +50295,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MOD_VER-131</t>
+          <t>MOD_VER-162</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -50319,12 +50310,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Exploring RAGs Applications in Healthcare</t>
+          <t>HYPER-RAG: Evaluating Hyperparameter Trade-Offs in Biomedical Retrieval-Augmented Generation</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/FLLM67465.2025.11391150</t>
+          <t>https://doi.org/10.1109/PuneCon67554.2025.11377827</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -50341,7 +50332,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MOD_VER-132</t>
+          <t>MOD_VER-165</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -50356,12 +50347,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SearchRAG: Can Search Engines Be Helpful for LLM-Based Medical Question Answering?</t>
+          <t>MedRAGShield: A Three-Tier Defense Framework Against Document Poisoning and Adversarial Attacks in Medical Retrieval-Augmented Generation Systems</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/BIBM66473.2025.11356025</t>
+          <t>https://doi.org/10.1109/ICESST69086.2026.11582854</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -50378,7 +50369,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MOD_VER-137</t>
+          <t>MOD_VER-167</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -50393,12 +50384,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>From Confidence to Care: Rule-Based Escalation for Trustworthy Clinical AI</t>
+          <t>Evaluating the Reliability and Utility of GPT-4o as a Medical Expert Across Different Interaction Modes</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/CASCON66301.2025.00097</t>
+          <t>https://doi.org/10.1109/BIBM66473.2025.11356967</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -50415,7 +50406,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MOD_VER-138</t>
+          <t>MOD_VER-168</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -50430,12 +50421,12 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Sanity-LLM: Enhancing Mental Health Chatbots with Retrieval-Augmented Generation (RAG)</t>
+          <t>RAGNet: Enhancing Conversational AI in Medical Domain</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICIMCIS68501.2025.11327020</t>
+          <t>https://doi.org/10.1109/ICETM63734.2025.11051911</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -50452,7 +50443,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MOD_VER-139</t>
+          <t>MOD_VER-169</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -50467,12 +50458,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Multimodal RAG Deployment Strategies for Medical Image Understanding: API-Based, Local Fine-Tuning, and Hybrid Approaches</t>
+          <t>RAGClin: A Privacy-Preserving Retrieval-Augmented Generation Framework for Clinical Question</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/AIxMHC65380.2025.00028</t>
+          <t>https://doi.org/10.1109/ICERECT65215.2025.11377112</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -50489,7 +50480,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MOD_VER-140</t>
+          <t>MOD_VER-170</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -50504,12 +50495,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Structured Multimodal RAG: Document-Aware Retrieval and Alignment for Hallucination Mitigation</t>
+          <t>Explainable GraphRAG: A Path-Based Interpretability Framework for Ontology-Grounded Clinical LLMs</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/AIAHPC66801.2025.11290404</t>
+          <t>https://doi.org/10.1109/3SCEA68071.2026.11603104</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -50526,7 +50517,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>MOD_VER-141</t>
+          <t>MOD_VER-172</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -50541,12 +50532,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AI Medical Health Assistant: Rag Approach</t>
+          <t>The Impact of Ontology Structure in the Performance of RAG Systems: a Medical Use Case</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/I2ITCON65200.2025.11210469</t>
+          <t>https://doi.org/10.1109/CAI68641.2026.11536252</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -50563,7 +50554,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>MOD_VER-143</t>
+          <t>MOD_VER-174</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -50578,12 +50569,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>AI-Driven Differential Diagnosis: Leveraging RAG and LLMs in Intelligent Healthcare Systems</t>
+          <t>Dynamic Retrieval Strategy for Summarizing Doctor–Patient Dialogues with RAG</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/IE64880.2025.11130125</t>
+          <t>https://doi.org/10.1109/BigData66926.2025.11402171</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -50600,7 +50591,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MOD_VER-144</t>
+          <t>MOD_VER-175</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -50615,12 +50606,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>A Tree-based RAG-Agent Recommendation System: A Case Study in Medical Test Data</t>
+          <t>CardioRAG: Toward Trustworthy Medical Question Answering Through Hypothetical Document and Instruction-Aware Embedding</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICCAI66501.2025.00106</t>
+          <t>https://doi.org/10.1109/ICHORA69329.2026.11537174</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -50637,7 +50628,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MOD_VER-148</t>
+          <t>MOD_VER-176</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -50652,12 +50643,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Impact of Knowledge Source Type on RAG-Based LLMs in Specialized Medical Domains: A Case Study on Systemic Lupus Erythematosus</t>
+          <t>Robustness of Question Answering Systems in the Biomedical Domain: a study of the BioASQ dataset</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/IAICT71158.2026.11620937</t>
+          <t>https://doi.org/10.1109/ICIT64950.2025.11049250</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -50674,7 +50665,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MOD_VER-149</t>
+          <t>MOD_VER-177</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -50689,12 +50680,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>RAG-Based Knowledge Retrieval Architecture for Medical Web Platforms</t>
+          <t>Vulnerabilities of a Medical and Scientific based RAG System</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ISADES69945.2026.11608242</t>
+          <t>https://doi.org/10.1109/ACTEA66485.2025.11189974</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -50711,7 +50702,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MOD_VER-151</t>
+          <t>MOD_VER-178</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -50726,12 +50717,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>ClinixAI – A Rag-Powered Medical Assistant with Verified Clinical Insights</t>
+          <t>A RAG-based Medical Assistant Especially for Infectious Diseases</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/ICADCS70036.2026.11582998</t>
+          <t>https://doi.org/10.1109/ICICT60155.2024.10544639</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -50740,598 +50731,6 @@
         </is>
       </c>
       <c r="G200" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>MOD_VER-152</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>Navigator: A Knowledge Graph and Agent-based Framework for Guiding Large Language Models toward Accurate and Reliable Medical Reasoning</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/CSCWD68734.2026.11581682</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>MOD_VER-154</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Design and Implementation of an Authoritative Medical QA System Based on Retrieval-Augmented Generation (RAG)</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/AIITA69518.2026.11567160</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>MOD_VER-156</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Adapting Large Language Models for Healthcare with an Enhanced Retrieval-Augmented Generation Framework</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICAACE65325.2025.11019949</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>MOD_VER-158</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>MediTriR: A Triple-Driven Approach to Retrieval-Augmented Generation for Medical Question Answering Tasks</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICSC64641.2025.00032</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>MOD_VER-162</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>HYPER-RAG: Evaluating Hyperparameter Trade-Offs in Biomedical Retrieval-Augmented Generation</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/PuneCon67554.2025.11377827</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>MOD_VER-165</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>MedRAGShield: A Three-Tier Defense Framework Against Document Poisoning and Adversarial Attacks in Medical Retrieval-Augmented Generation Systems</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICESST69086.2026.11582854</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>MOD_VER-167</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Evaluating the Reliability and Utility of GPT-4o as a Medical Expert Across Different Interaction Modes</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/BIBM66473.2025.11356967</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>MOD_VER-168</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>RAGNet: Enhancing Conversational AI in Medical Domain</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICETM63734.2025.11051911</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>MOD_VER-169</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>RAGClin: A Privacy-Preserving Retrieval-Augmented Generation Framework for Clinical Question</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICERECT65215.2025.11377112</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>MOD_VER-170</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Explainable GraphRAG: A Path-Based Interpretability Framework for Ontology-Grounded Clinical LLMs</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/3SCEA68071.2026.11603104</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>MOD_VER-172</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>The Impact of Ontology Structure in the Performance of RAG Systems: a Medical Use Case</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/CAI68641.2026.11536252</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>MOD_VER-174</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Dynamic Retrieval Strategy for Summarizing Doctor–Patient Dialogues with RAG</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/BigData66926.2025.11402171</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>MOD_VER-175</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>CardioRAG: Toward Trustworthy Medical Question Answering Through Hypothetical Document and Instruction-Aware Embedding</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICHORA69329.2026.11537174</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>MOD_VER-176</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>Robustness of Question Answering Systems in the Biomedical Domain: a study of the BioASQ dataset</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICIT64950.2025.11049250</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>MOD_VER-177</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Vulnerabilities of a Medical and Scientific based RAG System</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ACTEA66485.2025.11189974</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Agente Moderador-verificador (papers de LLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>MOD_VER-178</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Cribado</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Moderador-verificador</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>A RAG-based Medical Assistant Especially for Infectious Diseases</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/ICICT60155.2024.10544639</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
         <is>
           <t>Agente Moderador-verificador (papers de LLM)</t>
         </is>
